--- a/single-api/rule-api/swagger_modules.xlsx
+++ b/single-api/rule-api/swagger_modules.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="模块汇总" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RuleApi" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="模块汇总" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="RuleApi" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -556,9 +556,19 @@
         <v>1</v>
       </c>
       <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="3" t="n"/>
+      <c r="F2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>100% (1/1)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n"/>
@@ -576,9 +586,19 @@
         <v>10</v>
       </c>
       <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
+      <c r="F3" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>100% (10/10)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n"/>
@@ -596,9 +616,19 @@
         <v>5</v>
       </c>
       <c r="E4" s="3" t="n"/>
-      <c r="F4" s="3" t="n"/>
-      <c r="G4" s="3" t="n"/>
-      <c r="H4" s="3" t="n"/>
+      <c r="F4" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>100% (5/5)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n"/>
@@ -616,9 +646,19 @@
         <v>51</v>
       </c>
       <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="n"/>
-      <c r="H5" s="3" t="n"/>
+      <c r="F5" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>93%</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>55% (28/51)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n"/>
@@ -1156,9 +1196,19 @@
         <v>1</v>
       </c>
       <c r="E26" s="3" t="n"/>
-      <c r="F26" s="3" t="n"/>
-      <c r="G26" s="3" t="n"/>
-      <c r="H26" s="3" t="n"/>
+      <c r="F26" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>100% (1/1)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n"/>
@@ -1176,9 +1226,19 @@
         <v>10</v>
       </c>
       <c r="E27" s="3" t="n"/>
-      <c r="F27" s="3" t="n"/>
-      <c r="G27" s="3" t="n"/>
-      <c r="H27" s="3" t="n"/>
+      <c r="F27" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>100% (10/10)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n"/>
@@ -1196,9 +1256,19 @@
         <v>5</v>
       </c>
       <c r="E28" s="3" t="n"/>
-      <c r="F28" s="3" t="n"/>
-      <c r="G28" s="3" t="n"/>
-      <c r="H28" s="3" t="n"/>
+      <c r="F28" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>100% (5/5)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n"/>
@@ -4109,11 +4179,11 @@
       <c r="F2" s="3" t="n"/>
       <c r="G2" s="7" t="inlineStr">
         <is>
-          <t>手动触发规则消息（无ES流量）</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="16" customHeight="1">
+          <t>场景1: 默认调用(无入参)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="96" customHeight="1">
       <c r="A3" s="3" t="n"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
@@ -4138,7 +4208,12 @@
       <c r="F3" s="3" t="n"/>
       <c r="G3" s="7" t="inlineStr">
         <is>
-          <t>获取规则动作执行指标 — 100%</t>
+          <t>场景1: ruleType=Targeting
+场景2: ruleType=Placement
+场景3: ruleType=Auto Refill
+场景4: ruleType=Campaign
+场景5: ruleType=Audience
+场景6: ruleType=SOV Bid</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4242,7 @@
       <c r="F4" s="3" t="n"/>
       <c r="G4" s="7" t="inlineStr">
         <is>
-          <t>获取规则通知邮件列表 — 100%</t>
+          <t>场景1: 默认调用(无入参)</t>
         </is>
       </c>
     </row>
@@ -4196,7 +4271,7 @@
       <c r="F5" s="3" t="n"/>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>获取AddOn插件状态（无ES流量）</t>
+          <t>场景1: 默认调用(无入参)</t>
         </is>
       </c>
     </row>
@@ -4225,7 +4300,7 @@
       <c r="F6" s="3" t="n"/>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>获取商业化功能权限 — 100%</t>
+          <t>场景1: 默认调用(无入参)</t>
         </is>
       </c>
     </row>
@@ -4254,7 +4329,7 @@
       <c r="F7" s="3" t="n"/>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>开通AddOn插件 [NEEDS REAL VALUE]（无ES流量）</t>
+          <t>场景1: productLine=amazon</t>
         </is>
       </c>
     </row>
@@ -4283,7 +4358,7 @@
       <c r="F8" s="3" t="n"/>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>获取规则条件指标配置 — 100%</t>
+          <t>场景1: ruleType=Targeting(推断)</t>
         </is>
       </c>
     </row>
@@ -4312,7 +4387,7 @@
       <c r="F9" s="3" t="n"/>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>获取规则动作指标配置 — 100%</t>
+          <t>场景1: 默认调用(无入参)</t>
         </is>
       </c>
     </row>
@@ -4341,11 +4416,11 @@
       <c r="F10" s="3" t="n"/>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>保存自定义规则动作指标配置（无ES流量）</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="16" customHeight="1">
+          <t>场景1: productLine=amazon</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1">
       <c r="A11" s="3" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
@@ -4370,7 +4445,8 @@
       <c r="F11" s="3" t="n"/>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>获取规则类型枚举列表 — 100%</t>
+          <t>场景1: productLine=amazon筛选
+场景2: 不带productLine(旧版调用)</t>
         </is>
       </c>
     </row>
@@ -4399,7 +4475,7 @@
       <c r="F12" s="3" t="n"/>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>获取支持的时区列表 — 100%</t>
+          <t>场景1: 默认调用(无入参)</t>
         </is>
       </c>
     </row>
@@ -4428,7 +4504,7 @@
       <c r="F13" s="3" t="n"/>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>查询品牌/制造商数据（无ES流量）</t>
+          <t>场景1: productLine=amazon默认场景</t>
         </is>
       </c>
     </row>
@@ -4457,11 +4533,11 @@
       <c r="F14" s="3" t="n"/>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>查询数据影响分类（无ES流量）</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="16" customHeight="1">
+          <t>场景1: productLine=amazon</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="32" customHeight="1">
       <c r="A15" s="3" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
@@ -4486,7 +4562,8 @@
       <c r="F15" s="3" t="n"/>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>查询OOS ASIN列表 — 1%</t>
+          <t>场景1: 默认查询(不筛选retailer)
+场景2: 按retailer筛选</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4592,7 @@
       <c r="F16" s="3" t="n"/>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>查询OOS品牌列表 — 2%</t>
+          <t>场景1: productLine=amazon</t>
         </is>
       </c>
     </row>
@@ -4544,7 +4621,7 @@
       <c r="F17" s="3" t="n"/>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>查询价格ASIN列表 — 2%</t>
+          <t>场景1: productLine=amazon</t>
         </is>
       </c>
     </row>
@@ -4652,7 +4729,7 @@
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="16" customHeight="1">
       <c r="A22" s="3" t="n"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
@@ -4675,7 +4752,11 @@
         </is>
       </c>
       <c r="F22" s="3" t="n"/>
-      <c r="G22" s="3" t="n"/>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>场景1: 测试账号真实规则详情</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="16" customHeight="1">
       <c r="A23" s="3" t="n"/>
@@ -4777,7 +4858,7 @@
       <c r="F26" s="3" t="n"/>
       <c r="G26" s="3" t="n"/>
     </row>
-    <row r="27">
+    <row r="27" ht="16" customHeight="1">
       <c r="A27" s="3" t="n"/>
       <c r="B27" s="3" t="inlineStr">
         <is>
@@ -4800,9 +4881,13 @@
         </is>
       </c>
       <c r="F27" s="3" t="n"/>
-      <c r="G27" s="3" t="n"/>
-    </row>
-    <row r="28">
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>场景1: 测试账号真实profile[FAIL]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
       <c r="A28" s="3" t="n"/>
       <c r="B28" s="3" t="inlineStr">
         <is>
@@ -4825,7 +4910,11 @@
         </is>
       </c>
       <c r="F28" s="3" t="n"/>
-      <c r="G28" s="3" t="n"/>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>场景1: 每周执行时间计算</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n"/>
@@ -4881,7 +4970,7 @@
         </is>
       </c>
     </row>
-    <row r="31">
+    <row r="31" ht="16" customHeight="1">
       <c r="A31" s="3" t="n"/>
       <c r="B31" s="3" t="inlineStr">
         <is>
@@ -4904,7 +4993,11 @@
         </is>
       </c>
       <c r="F31" s="3" t="n"/>
-      <c r="G31" s="3" t="n"/>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>场景1: Auto Refill目标校验(测试账号真实campaign)</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="16" customHeight="1">
       <c r="A32" s="3" t="n"/>
@@ -4929,7 +5022,11 @@
         </is>
       </c>
       <c r="F32" s="3" t="n"/>
-      <c r="G32" s="3" t="n"/>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>场景1: 测试账号真实规则</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="32" customHeight="1">
       <c r="A33" s="3" t="n"/>
@@ -4956,12 +5053,11 @@
       <c r="F33" s="3" t="n"/>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>新建规则名称重复校验 — 80%
-编辑规则名称重复校验(创建临时规则,可重复) — 20%</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
+          <t>场景1: 检查未占用的规则名</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
       <c r="A34" s="3" t="n"/>
       <c r="B34" s="3" t="inlineStr">
         <is>
@@ -4984,7 +5080,11 @@
         </is>
       </c>
       <c r="F34" s="3" t="n"/>
-      <c r="G34" s="3" t="n"/>
+      <c r="G34" s="7" t="inlineStr">
+        <is>
+          <t>场景1: 默认调用(无入参)</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="32" customHeight="1">
       <c r="A35" s="3" t="n"/>
@@ -5009,7 +5109,11 @@
         </is>
       </c>
       <c r="F35" s="3" t="n"/>
-      <c r="G35" s="3" t="n"/>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>场景1: 按客户维度日期段报表</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n"/>
@@ -5090,7 +5194,7 @@
         </is>
       </c>
     </row>
-    <row r="39">
+    <row r="39" ht="16" customHeight="1">
       <c r="A39" s="3" t="n"/>
       <c r="B39" s="3" t="inlineStr">
         <is>
@@ -5113,7 +5217,11 @@
         </is>
       </c>
       <c r="F39" s="3" t="n"/>
-      <c r="G39" s="3" t="n"/>
+      <c r="G39" s="7" t="inlineStr">
+        <is>
+          <t>场景1: 导出规则列表(Auto模式,按创建时间排序)</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="16" customHeight="1">
       <c r="A40" s="3" t="n"/>
@@ -5138,9 +5246,13 @@
         </is>
       </c>
       <c r="F40" s="3" t="n"/>
-      <c r="G40" s="3" t="n"/>
-    </row>
-    <row r="41">
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>场景1: 导出客户维度报表(构造)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
       <c r="A41" s="3" t="n"/>
       <c r="B41" s="3" t="inlineStr">
         <is>
@@ -5163,7 +5275,11 @@
         </is>
       </c>
       <c r="F41" s="3" t="n"/>
-      <c r="G41" s="3" t="n"/>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>场景1: 默认列表查询(构造)</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="16" customHeight="1">
       <c r="A42" s="3" t="n"/>
@@ -5190,11 +5306,11 @@
       <c r="F42" s="3" t="n"/>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>查询规则应用列表 — 100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
+          <t>场景1: 按owner查询已应用规则ID列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="16" customHeight="1">
       <c r="A43" s="3" t="n"/>
       <c r="B43" s="3" t="inlineStr">
         <is>
@@ -5217,7 +5333,11 @@
         </is>
       </c>
       <c r="F43" s="3" t="n"/>
-      <c r="G43" s="3" t="n"/>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>场景1: 按测试账号真实target查询</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="16" customHeight="1">
       <c r="A44" s="3" t="n"/>
@@ -5242,9 +5362,13 @@
         </is>
       </c>
       <c r="F44" s="3" t="n"/>
-      <c r="G44" s="3" t="n"/>
-    </row>
-    <row r="45">
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>场景1: 按profile查询</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="16" customHeight="1">
       <c r="A45" s="3" t="n"/>
       <c r="B45" s="3" t="inlineStr">
         <is>
@@ -5267,9 +5391,13 @@
         </is>
       </c>
       <c r="F45" s="3" t="n"/>
-      <c r="G45" s="3" t="n"/>
-    </row>
-    <row r="46">
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>场景1: 按client查询</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="16" customHeight="1">
       <c r="A46" s="3" t="n"/>
       <c r="B46" s="3" t="inlineStr">
         <is>
@@ -5292,7 +5420,11 @@
         </is>
       </c>
       <c r="F46" s="3" t="n"/>
-      <c r="G46" s="3" t="n"/>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>场景1: 按client查询</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="16" customHeight="1">
       <c r="A47" s="3" t="n"/>
@@ -5319,11 +5451,11 @@
       <c r="F47" s="3" t="n"/>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>查询AutoRefill规则关联profile — 100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
+          <t>场景1: 默认调用(无入参)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="16" customHeight="1">
       <c r="A48" s="3" t="n"/>
       <c r="B48" s="3" t="inlineStr">
         <is>
@@ -5346,7 +5478,11 @@
         </is>
       </c>
       <c r="F48" s="3" t="n"/>
-      <c r="G48" s="3" t="n"/>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>场景1: 按测试账号真实campaign查询</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="48" customHeight="1">
       <c r="A49" s="3" t="n"/>
@@ -5373,61 +5509,4225 @@
       <c r="F49" s="3" t="n"/>
       <c r="G49" s="7" t="inlineStr">
         <is>
+          <t>场景1: 默认查询(不带userIds过滤)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="16" customHeight="1">
+      <c r="A50" s="3" t="n"/>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>/definition/getProfile</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="n"/>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>场景1: 默认查询(构造)[FAIL]</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="48" customHeight="1">
+      <c r="A51" s="3" t="n"/>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>/definition/getRule</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="n"/>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>场景1: 默认列表浏览(按创建时间倒序)
+场景2: 按ruleType=Campaign过滤</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="16" customHeight="1">
+      <c r="A52" s="3" t="n"/>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>/definition/getRuleInfoByCampaignId</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="n"/>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>场景1: 测试账号真实campaign</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="48" customHeight="1">
+      <c r="A53" s="3" t="n"/>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>/definition/getRuleTargetInfo</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="n"/>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>场景1: ruleId=测试账号真实规则</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="16" customHeight="1">
+      <c r="A54" s="3" t="n"/>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>/definition/getRuleTargetInfoByRuleIds</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="n"/>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>场景1: 测试账号真实规则ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="16" customHeight="1">
+      <c r="A55" s="3" t="n"/>
+      <c r="B55" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="D55" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>/definition/getTarget</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="n"/>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>场景1: 默认查询(构造)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="16" customHeight="1">
+      <c r="A56" s="3" t="n"/>
+      <c r="B56" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>/definition/hasClickHitMode</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="n"/>
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>场景1: 默认调用(不带mode)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="16" customHeight="1">
+      <c r="A57" s="3" t="n"/>
+      <c r="B57" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C57" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="D57" s="3" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>/definition/transferableOwnerList</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="n"/>
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>场景1: 默认调用(无入参)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="16" customHeight="1">
+      <c r="A58" s="3" t="n"/>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>/definition/updateAppliedObj</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="n"/>
+      <c r="G58" s="7" t="inlineStr">
+        <is>
+          <t>更新规则应用对象(创建临时规则,可重复) — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="16" customHeight="1">
+      <c r="A59" s="3" t="n"/>
+      <c r="B59" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>/definition/updateAutomation</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="n"/>
+      <c r="G59" s="3" t="n"/>
+    </row>
+    <row r="60" ht="16" customHeight="1">
+      <c r="A60" s="3" t="n"/>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>/downloadMapping</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="n"/>
+      <c r="G60" s="3" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="n"/>
+      <c r="B61" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C61" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="D61" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>/downloadMapping/{id}</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="n"/>
+      <c r="G61" s="3" t="n"/>
+    </row>
+    <row r="62" ht="16" customHeight="1">
+      <c r="A62" s="3" t="n"/>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>/getRuleViewList</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="n"/>
+      <c r="G62" s="7" t="inlineStr">
+        <is>
+          <t>场景1: 按测试账号真实规则ID查询</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="n"/>
+      <c r="B63" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C63" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="D63" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>/terminatedClientRule</t>
+        </is>
+      </c>
+      <c r="F63" s="3" t="n"/>
+      <c r="G63" s="3" t="n"/>
+    </row>
+    <row r="64" ht="16" customHeight="1">
+      <c r="A64" s="3" t="n"/>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>feature-usage-controller</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>/featureHealth/monthlyReport</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="n"/>
+      <c r="G64" s="7" t="inlineStr">
+        <is>
+          <t>walmart平台月度功能使用报告 — 2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="16" customHeight="1">
+      <c r="A65" s="3" t="n"/>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>feature-usage-controller</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>/featureHealth/topNClients</t>
+        </is>
+      </c>
+      <c r="F65" s="3" t="n"/>
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>amazon平台Top N客户功能使用排行 — 2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="32" customHeight="1">
+      <c r="A66" s="3" t="n"/>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>health-controller</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>/health</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="n"/>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>服务健康检查（无ES流量）</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="16" customHeight="1">
+      <c r="A67" s="3" t="n"/>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>history-controller</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
+        <is>
+          <t>/changeSuggestionStatus</t>
+        </is>
+      </c>
+      <c r="F67" s="3" t="n"/>
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>变更建议操作状态[需实际建议记录]（无ES流量）</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="16" customHeight="1">
+      <c r="A68" s="3" t="n"/>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>history-controller</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>/getAdGroups/{ruleExecutionLogId}</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="n"/>
+      <c r="G68" s="7" t="inlineStr">
+        <is>
+          <t>执行日志AdGroup列表（无ES流量）</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="16" customHeight="1">
+      <c r="A69" s="3" t="n"/>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>history-controller</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E69" s="3" t="inlineStr">
+        <is>
+          <t>/getAdtomicSuggestions</t>
+        </is>
+      </c>
+      <c r="F69" s="3" t="n"/>
+      <c r="G69" s="7" t="inlineStr">
+        <is>
+          <t>Adtomic建议操作列表（无ES流量）</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="16" customHeight="1">
+      <c r="A70" s="3" t="n"/>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>history-controller</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>/getAutoRuleDetailLog</t>
+        </is>
+      </c>
+      <c r="F70" s="3" t="n"/>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>自动规则详情日志[Amazon专属]（无ES流量）</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="16" customHeight="1">
+      <c r="A71" s="3" t="n"/>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>history-controller</t>
+        </is>
+      </c>
+      <c r="D71" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>/getAutoRuleDetailLogFilter</t>
+        </is>
+      </c>
+      <c r="F71" s="3" t="n"/>
+      <c r="G71" s="7" t="inlineStr">
+        <is>
+          <t>自动规则日志过滤器[Amazon专属]（无ES流量）</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="16" customHeight="1">
+      <c r="A72" s="3" t="n"/>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>history-controller</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>/getAutoRuleLogList</t>
+        </is>
+      </c>
+      <c r="F72" s="3" t="n"/>
+      <c r="G72" s="7" t="inlineStr">
+        <is>
+          <t>自动规则执行日志列表[Amazon专属]（无ES流量）</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="16" customHeight="1">
+      <c r="A73" s="3" t="n"/>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>history-controller</t>
+        </is>
+      </c>
+      <c r="D73" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E73" s="3" t="inlineStr">
+        <is>
+          <t>/getCampaigns/{ruleExecutionLogId}</t>
+        </is>
+      </c>
+      <c r="F73" s="3" t="n"/>
+      <c r="G73" s="7" t="inlineStr">
+        <is>
+          <t>执行日志Campaign列表 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="16" customHeight="1">
+      <c r="A74" s="3" t="n"/>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>history-controller</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>/getCampaignTags/{ruleExecutionLogId}</t>
+        </is>
+      </c>
+      <c r="F74" s="3" t="n"/>
+      <c r="G74" s="7" t="inlineStr">
+        <is>
+          <t>执行日志CampaignTag列表 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="16" customHeight="1">
+      <c r="A75" s="3" t="n"/>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>history-controller</t>
+        </is>
+      </c>
+      <c r="D75" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>/getDetail/{ruleExecutionLogId}</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="n"/>
+      <c r="G75" s="7" t="inlineStr">
+        <is>
+          <t>执行日志详情[需TikTok执行历史]（无ES流量）</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="16" customHeight="1">
+      <c r="A76" s="3" t="n"/>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>history-controller</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>/getHistoryList</t>
+        </is>
+      </c>
+      <c r="F76" s="3" t="n"/>
+      <c r="G76" s="7" t="inlineStr">
+        <is>
+          <t>历史执行记录列表 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="16" customHeight="1">
+      <c r="A77" s="3" t="n"/>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C77" s="3" t="inlineStr">
+        <is>
+          <t>history-controller</t>
+        </is>
+      </c>
+      <c r="D77" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E77" s="3" t="inlineStr">
+        <is>
+          <t>/getLineItems/{ruleExecutionLogId}</t>
+        </is>
+      </c>
+      <c r="F77" s="3" t="n"/>
+      <c r="G77" s="7" t="inlineStr">
+        <is>
+          <t>执行日志LineItem列表（无ES流量）</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="16" customHeight="1">
+      <c r="A78" s="3" t="n"/>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>history-controller</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>/getPendingList</t>
+        </is>
+      </c>
+      <c r="F78" s="3" t="n"/>
+      <c r="G78" s="7" t="inlineStr">
+        <is>
+          <t>待处理规则列表 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="16" customHeight="1">
+      <c r="A79" s="3" t="n"/>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>history-controller</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>/getPendingRuleNum</t>
+        </is>
+      </c>
+      <c r="F79" s="3" t="n"/>
+      <c r="G79" s="7" t="inlineStr">
+        <is>
+          <t>待处理规则数量 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="16" customHeight="1">
+      <c r="A80" s="3" t="n"/>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>history-controller</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>/getProducts/{ruleExecutionLogId}</t>
+        </is>
+      </c>
+      <c r="F80" s="3" t="n"/>
+      <c r="G80" s="7" t="inlineStr">
+        <is>
+          <t>执行日志Product列表（无ES流量）</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="16" customHeight="1">
+      <c r="A81" s="3" t="n"/>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C81" s="3" t="inlineStr">
+        <is>
+          <t>history-controller</t>
+        </is>
+      </c>
+      <c r="D81" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>/getProfiles</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="n"/>
+      <c r="G81" s="7" t="inlineStr">
+        <is>
+          <t>执行日志Profile列表 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="16" customHeight="1">
+      <c r="A82" s="3" t="n"/>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>history-controller</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>/history/archiveOldLogsTask</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="n"/>
+      <c r="G82" s="7" t="inlineStr">
+        <is>
+          <t>归档旧日志（运维接口）（无ES流量）</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="16" customHeight="1">
+      <c r="A83" s="3" t="n"/>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>history-controller</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>/history/deleteHistoryData/{tableName}</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="n"/>
+      <c r="G83" s="7" t="inlineStr">
+        <is>
+          <t>清理历史数据（运维接口） — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="16" customHeight="1">
+      <c r="A84" s="3" t="n"/>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>history-controller</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>/history/export/{ruleExecutionLogId}</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="n"/>
+      <c r="G84" s="7" t="inlineStr">
+        <is>
+          <t>导出执行日志[需TikTok执行历史]（无ES流量）</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="16" customHeight="1">
+      <c r="A85" s="3" t="n"/>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C85" s="3" t="inlineStr">
+        <is>
+          <t>history-controller</t>
+        </is>
+      </c>
+      <c r="D85" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E85" s="3" t="inlineStr">
+        <is>
+          <t>/history/getLastPauseAsins/{ruleId}</t>
+        </is>
+      </c>
+      <c r="F85" s="3" t="n"/>
+      <c r="G85" s="7" t="inlineStr">
+        <is>
+          <t>规则最近暂停ASIN列表（无ES流量）</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="16" customHeight="1">
+      <c r="A86" s="3" t="n"/>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>history-controller</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>/history/getRuleAlertCount</t>
+        </is>
+      </c>
+      <c r="F86" s="3" t="n"/>
+      <c r="G86" s="7" t="inlineStr">
+        <is>
+          <t>标准告警计数查询 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="16" customHeight="1">
+      <c r="A87" s="3" t="n"/>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C87" s="3" t="inlineStr">
+        <is>
+          <t>history-controller</t>
+        </is>
+      </c>
+      <c r="D87" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E87" s="3" t="inlineStr">
+        <is>
+          <t>/history/getRuleAlertDetail</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="n"/>
+      <c r="G87" s="7" t="inlineStr">
+        <is>
+          <t>规则告警详情列表 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="16" customHeight="1">
+      <c r="A88" s="3" t="n"/>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>history-controller</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>/history/getRuleDeadDetail</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="n"/>
+      <c r="G88" s="7" t="inlineStr">
+        <is>
+          <t>规则失效详情（无ES流量）</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="16" customHeight="1">
+      <c r="A89" s="3" t="n"/>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C89" s="3" t="inlineStr">
+        <is>
+          <t>history-controller</t>
+        </is>
+      </c>
+      <c r="D89" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E89" s="3" t="inlineStr">
+        <is>
+          <t>/pending/export/{ruleExecutionLogId}</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="n"/>
+      <c r="G89" s="7" t="inlineStr">
+        <is>
+          <t>导出待处理列表[需TikTok执行历史]（无ES流量）</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="16" customHeight="1">
+      <c r="A90" s="3" t="n"/>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>history-controller</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>/queryRuleSnapshots</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="n"/>
+      <c r="G90" s="7" t="inlineStr">
+        <is>
+          <t>规则快照查询 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="16" customHeight="1">
+      <c r="A91" s="3" t="n"/>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>history-controller</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="inlineStr">
+        <is>
+          <t>/setIgnored</t>
+        </is>
+      </c>
+      <c r="F91" s="3" t="n"/>
+      <c r="G91" s="7" t="inlineStr">
+        <is>
+          <t>设置忽略操作[需TikTok执行历史]（无ES流量）</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="16" customHeight="1">
+      <c r="A92" s="3" t="n"/>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>history-controller</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>/setRemarks</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="n"/>
+      <c r="G92" s="7" t="inlineStr">
+        <is>
+          <t>设置执行日志备注[需TikTok执行历史]（无ES流量）</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="16" customHeight="1">
+      <c r="A93" s="3" t="n"/>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>migration-controller</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="inlineStr">
+        <is>
+          <t>/migration/amazon/targetingType</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="n"/>
+      <c r="G93" s="7" t="inlineStr">
+        <is>
+          <t>Amazon定向类型迁移（无ES流量）</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="16" customHeight="1">
+      <c r="A94" s="3" t="n"/>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>migration-controller</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>/migration/kroger-to-krogerv3</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="n"/>
+      <c r="G94" s="7" t="inlineStr">
+        <is>
+          <t>Kroger迁移至KrogerV3 — 2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="16" customHeight="1">
+      <c r="A95" s="3" t="n"/>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C95" s="3" t="inlineStr">
+        <is>
+          <t>migration-controller</t>
+        </is>
+      </c>
+      <c r="D95" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E95" s="3" t="inlineStr">
+        <is>
+          <t>/migration/single-to-multi-action</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="n"/>
+      <c r="G95" s="7" t="inlineStr">
+        <is>
+          <t>单动作迁移至多动作（无ES流量）</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="16" customHeight="1">
+      <c r="A96" s="3" t="n"/>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>report-controller</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>/profitero/getProfiteroCountryList</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="n"/>
+      <c r="G96" s="7" t="inlineStr">
+        <is>
+          <t>获取Profitero国家列表 — 52%</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="16" customHeight="1">
+      <c r="A97" s="3" t="n"/>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>report-controller</t>
+        </is>
+      </c>
+      <c r="D97" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>/report/BrandEventList</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="n"/>
+      <c r="G97" s="7" t="inlineStr">
+        <is>
+          <t>walmart平台品牌事件列表 — 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="16" customHeight="1">
+      <c r="A98" s="3" t="n"/>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
+        <is>
+          <t>report-controller</t>
+        </is>
+      </c>
+      <c r="D98" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E98" s="3" t="inlineStr">
+        <is>
+          <t>/report/CompetitorBrandSummary</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="n"/>
+      <c r="G98" s="7" t="inlineStr">
+        <is>
+          <t>walmart平台竞争品牌汇总</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="16" customHeight="1">
+      <c r="A99" s="3" t="n"/>
+      <c r="B99" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>report-controller</t>
+        </is>
+      </c>
+      <c r="D99" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E99" s="3" t="inlineStr">
+        <is>
+          <t>/report/ExecutionRecordSummary</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="n"/>
+      <c r="G99" s="7" t="inlineStr">
+        <is>
+          <t>target平台执行记录汇总 — 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="16" customHeight="1">
+      <c r="A100" s="3" t="n"/>
+      <c r="B100" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
+        <is>
+          <t>report-controller</t>
+        </is>
+      </c>
+      <c r="D100" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>/report/getAllBrands</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="n"/>
+      <c r="G100" s="7" t="inlineStr">
+        <is>
+          <t>walmart平台获取所有品牌</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="16" customHeight="1">
+      <c r="A101" s="3" t="n"/>
+      <c r="B101" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C101" s="3" t="inlineStr">
+        <is>
+          <t>report-controller</t>
+        </is>
+      </c>
+      <c r="D101" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>/report/getAllProfiteroRules</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="n"/>
+      <c r="G101" s="7" t="inlineStr">
+        <is>
+          <t>获取所有Profitero规则</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="16" customHeight="1">
+      <c r="A102" s="3" t="n"/>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C102" s="3" t="inlineStr">
+        <is>
+          <t>report-controller</t>
+        </is>
+      </c>
+      <c r="D102" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E102" s="3" t="inlineStr">
+        <is>
+          <t>/report/getAllProfiteroRulesApplies</t>
+        </is>
+      </c>
+      <c r="F102" s="3" t="n"/>
+      <c r="G102" s="7" t="inlineStr">
+        <is>
+          <t>查询Profitero规则应用记录 — 7%</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="16" customHeight="1">
+      <c r="A103" s="3" t="n"/>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>report-controller</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>/report/getAsins</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="n"/>
+      <c r="G103" s="7" t="inlineStr">
+        <is>
+          <t>walmart平台获取ASIN列表 — 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="16" customHeight="1">
+      <c r="A104" s="3" t="n"/>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>report-controller</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="inlineStr">
+        <is>
+          <t>/report/getDailyRuleData</t>
+        </is>
+      </c>
+      <c r="F104" s="3" t="n"/>
+      <c r="G104" s="7" t="inlineStr">
+        <is>
+          <t>查询每日规则数据</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="16" customHeight="1">
+      <c r="A105" s="3" t="n"/>
+      <c r="B105" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C105" s="3" t="inlineStr">
+        <is>
+          <t>report-controller</t>
+        </is>
+      </c>
+      <c r="D105" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>/report/getSignals</t>
+        </is>
+      </c>
+      <c r="F105" s="3" t="n"/>
+      <c r="G105" s="7" t="inlineStr">
+        <is>
+          <t>amazon平台获取信号数据 — 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="16" customHeight="1">
+      <c r="A106" s="3" t="n"/>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>report-controller</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>/report/MyBrandCountSummary</t>
+        </is>
+      </c>
+      <c r="F106" s="3" t="n"/>
+      <c r="G106" s="7" t="inlineStr">
+        <is>
+          <t>target平台我的品牌数量汇总 — 6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="16" customHeight="1">
+      <c r="A107" s="3" t="n"/>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>report-controller</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="inlineStr">
+        <is>
+          <t>/report/syncBrands</t>
+        </is>
+      </c>
+      <c r="F107" s="3" t="n"/>
+      <c r="G107" s="7" t="inlineStr">
+        <is>
+          <t>同步品牌数据 — 16%</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="16" customHeight="1">
+      <c r="A108" s="3" t="n"/>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C108" s="3" t="inlineStr">
+        <is>
+          <t>report-controller</t>
+        </is>
+      </c>
+      <c r="D108" s="3" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>/report/syncTables</t>
+        </is>
+      </c>
+      <c r="F108" s="3" t="n"/>
+      <c r="G108" s="7" t="inlineStr">
+        <is>
+          <t>同步表格数据 — 16%</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="16" customHeight="1">
+      <c r="A109" s="3" t="n"/>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>share-pass-controller</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>/sharePass/check</t>
+        </is>
+      </c>
+      <c r="F109" s="3" t="n"/>
+      <c r="G109" s="7" t="inlineStr">
+        <is>
+          <t>校验共享通行证有效性 — 12%</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="16" customHeight="1">
+      <c r="A110" s="3" t="n"/>
+      <c r="B110" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>share-pass-controller</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="inlineStr">
+        <is>
+          <t>/sharePass/create</t>
+        </is>
+      </c>
+      <c r="F110" s="3" t="n"/>
+      <c r="G110" s="7" t="inlineStr">
+        <is>
+          <t>创建共享通行证后删除（可重复） — 8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="16" customHeight="1">
+      <c r="A111" s="3" t="n"/>
+      <c r="B111" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C111" s="3" t="inlineStr">
+        <is>
+          <t>share-pass-controller</t>
+        </is>
+      </c>
+      <c r="D111" s="3" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>/sharePass/creators</t>
+        </is>
+      </c>
+      <c r="F111" s="3" t="n"/>
+      <c r="G111" s="7" t="inlineStr">
+        <is>
+          <t>获取创建者列表 — 23%</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="n"/>
+      <c r="B112" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C112" s="3" t="inlineStr">
+        <is>
+          <t>share-pass-controller</t>
+        </is>
+      </c>
+      <c r="D112" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>/sharePass/delete</t>
+        </is>
+      </c>
+      <c r="F112" s="3" t="n"/>
+      <c r="G112" s="3" t="n"/>
+    </row>
+    <row r="113" ht="16" customHeight="1">
+      <c r="A113" s="3" t="n"/>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C113" s="3" t="inlineStr">
+        <is>
+          <t>share-pass-controller</t>
+        </is>
+      </c>
+      <c r="D113" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E113" s="3" t="inlineStr">
+        <is>
+          <t>/sharePass/edit</t>
+        </is>
+      </c>
+      <c r="F113" s="3" t="n"/>
+      <c r="G113" s="7" t="inlineStr">
+        <is>
+          <t>编辑共享通行证（无ES流量）</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="16" customHeight="1">
+      <c r="A114" s="3" t="n"/>
+      <c r="B114" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C114" s="3" t="inlineStr">
+        <is>
+          <t>share-pass-controller</t>
+        </is>
+      </c>
+      <c r="D114" s="3" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E114" s="3" t="inlineStr">
+        <is>
+          <t>/sharePass/getAccounts</t>
+        </is>
+      </c>
+      <c r="F114" s="3" t="n"/>
+      <c r="G114" s="7" t="inlineStr">
+        <is>
+          <t>获取可共享账户列表 — 25%</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="16" customHeight="1">
+      <c r="A115" s="3" t="n"/>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C115" s="3" t="inlineStr">
+        <is>
+          <t>share-pass-controller</t>
+        </is>
+      </c>
+      <c r="D115" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>/sharePass/getRuleIdsFromSharePass</t>
+        </is>
+      </c>
+      <c r="F115" s="3" t="n"/>
+      <c r="G115" s="7" t="inlineStr">
+        <is>
+          <t>通过共享通行证获取规则ID列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="16" customHeight="1">
+      <c r="A116" s="3" t="n"/>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>share-pass-controller</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="inlineStr">
+        <is>
+          <t>/sharePass/getSharePlatforms</t>
+        </is>
+      </c>
+      <c r="F116" s="3" t="n"/>
+      <c r="G116" s="7" t="inlineStr">
+        <is>
+          <t>获取可共享平台列表 — 8%</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="16" customHeight="1">
+      <c r="A117" s="3" t="n"/>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C117" s="3" t="inlineStr">
+        <is>
+          <t>share-pass-controller</t>
+        </is>
+      </c>
+      <c r="D117" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>/sharePass/list</t>
+        </is>
+      </c>
+      <c r="F117" s="3" t="n"/>
+      <c r="G117" s="7" t="inlineStr">
+        <is>
+          <t>amazon平台分页查询共享通行证列表 — 24%</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="16" customHeight="1">
+      <c r="A118" s="3" t="n"/>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t>template-controller</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
+          <t>/template</t>
+        </is>
+      </c>
+      <c r="F118" s="3" t="n"/>
+      <c r="G118" s="7" t="inlineStr">
+        <is>
+          <t>创建模板并批量创建(可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="16" customHeight="1">
+      <c r="A119" s="3" t="n"/>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>template-controller</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="inlineStr">
+        <is>
+          <t>/template/{templateId}</t>
+        </is>
+      </c>
+      <c r="F119" s="3" t="n"/>
+      <c r="G119" s="7" t="inlineStr">
+        <is>
+          <t>删除模板（需有效templateId）</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="16" customHeight="1">
+      <c r="A120" s="3" t="n"/>
+      <c r="B120" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C120" s="3" t="inlineStr">
+        <is>
+          <t>template-controller</t>
+        </is>
+      </c>
+      <c r="D120" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E120" s="3" t="inlineStr">
+        <is>
+          <t>/template/addFavorite</t>
+        </is>
+      </c>
+      <c r="F120" s="3" t="n"/>
+      <c r="G120" s="7" t="inlineStr">
+        <is>
+          <t>模板收藏切换</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="n"/>
+      <c r="B121" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C121" s="3" t="inlineStr">
+        <is>
+          <t>template-controller</t>
+        </is>
+      </c>
+      <c r="D121" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>/template/bulk</t>
+        </is>
+      </c>
+      <c r="F121" s="3" t="n"/>
+      <c r="G121" s="3" t="n"/>
+    </row>
+    <row r="122" ht="16" customHeight="1">
+      <c r="A122" s="3" t="n"/>
+      <c r="B122" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C122" s="3" t="inlineStr">
+        <is>
+          <t>template-controller</t>
+        </is>
+      </c>
+      <c r="D122" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E122" s="3" t="inlineStr">
+        <is>
+          <t>/template/category</t>
+        </is>
+      </c>
+      <c r="F122" s="3" t="n"/>
+      <c r="G122" s="7" t="inlineStr">
+        <is>
+          <t>创建编辑删除分类(可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="n"/>
+      <c r="B123" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C123" s="3" t="inlineStr">
+        <is>
+          <t>template-controller</t>
+        </is>
+      </c>
+      <c r="D123" s="3" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="E123" s="3" t="inlineStr">
+        <is>
+          <t>/template/category/{categoryId}</t>
+        </is>
+      </c>
+      <c r="F123" s="3" t="n"/>
+      <c r="G123" s="3" t="n"/>
+    </row>
+    <row r="124" ht="16" customHeight="1">
+      <c r="A124" s="3" t="n"/>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>template-controller</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="inlineStr">
+        <is>
+          <t>/template/default/{templateId}</t>
+        </is>
+      </c>
+      <c r="F124" s="3" t="n"/>
+      <c r="G124" s="7" t="inlineStr">
+        <is>
+          <t>默认模板/分类删除接口覆盖</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="n"/>
+      <c r="B125" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C125" s="3" t="inlineStr">
+        <is>
+          <t>template-controller</t>
+        </is>
+      </c>
+      <c r="D125" s="3" t="inlineStr">
+        <is>
+          <t>DELETE</t>
+        </is>
+      </c>
+      <c r="E125" s="3" t="inlineStr">
+        <is>
+          <t>/template/defaultCategory/{categoryId}</t>
+        </is>
+      </c>
+      <c r="F125" s="3" t="n"/>
+      <c r="G125" s="3" t="n"/>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="n"/>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>template-controller</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="inlineStr">
+        <is>
+          <t>/template/editCategory</t>
+        </is>
+      </c>
+      <c r="F126" s="3" t="n"/>
+      <c r="G126" s="3" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="n"/>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>template-controller</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="inlineStr">
+        <is>
+          <t>/template/editDefaultCategory</t>
+        </is>
+      </c>
+      <c r="F127" s="3" t="n"/>
+      <c r="G127" s="3" t="n"/>
+    </row>
+    <row r="128" ht="16" customHeight="1">
+      <c r="A128" s="3" t="n"/>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C128" s="3" t="inlineStr">
+        <is>
+          <t>template-controller</t>
+        </is>
+      </c>
+      <c r="D128" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E128" s="3" t="inlineStr">
+        <is>
+          <t>/template/editDefaultTemplate</t>
+        </is>
+      </c>
+      <c r="F128" s="3" t="n"/>
+      <c r="G128" s="7" t="inlineStr">
+        <is>
+          <t>查询并尝试编辑系统默认模板</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="16" customHeight="1">
+      <c r="A129" s="3" t="n"/>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>template-controller</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="inlineStr">
+        <is>
+          <t>/template/editTemplate</t>
+        </is>
+      </c>
+      <c r="F129" s="3" t="n"/>
+      <c r="G129" s="7" t="inlineStr">
+        <is>
+          <t>创建模板并验证editTemplate端点可达(可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="32" customHeight="1">
+      <c r="A130" s="3" t="n"/>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C130" s="3" t="inlineStr">
+        <is>
+          <t>template-controller</t>
+        </is>
+      </c>
+      <c r="D130" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>/template/getCategory</t>
+        </is>
+      </c>
+      <c r="F130" s="3" t="n"/>
+      <c r="G130" s="7" t="inlineStr">
+        <is>
+          <t>无ruleType过滤查询全部分类 — 40%
+Targeting类型模板分类 — 40%</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="16" customHeight="1">
+      <c r="A131" s="3" t="n"/>
+      <c r="B131" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>template-controller</t>
+        </is>
+      </c>
+      <c r="D131" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E131" s="3" t="inlineStr">
+        <is>
+          <t>/template/getDefaultCategory</t>
+        </is>
+      </c>
+      <c r="F131" s="3" t="n"/>
+      <c r="G131" s="7" t="inlineStr">
+        <is>
+          <t>获取默认模板分类 — 0.11%</t>
+        </is>
+      </c>
+    </row>
+    <row r="132" ht="16" customHeight="1">
+      <c r="A132" s="3" t="n"/>
+      <c r="B132" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>template-controller</t>
+        </is>
+      </c>
+      <c r="D132" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E132" s="3" t="inlineStr">
+        <is>
+          <t>/template/getDefaultTemplate</t>
+        </is>
+      </c>
+      <c r="F132" s="3" t="n"/>
+      <c r="G132" s="7" t="inlineStr">
+        <is>
+          <t>获取默认模板列表 — 0.15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="16" customHeight="1">
+      <c r="A133" s="3" t="n"/>
+      <c r="B133" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C133" s="3" t="inlineStr">
+        <is>
+          <t>template-controller</t>
+        </is>
+      </c>
+      <c r="D133" s="3" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>/template/getOwners</t>
+        </is>
+      </c>
+      <c r="F133" s="3" t="n"/>
+      <c r="G133" s="7" t="inlineStr">
+        <is>
+          <t>获取模板创建者列表 — 3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="n"/>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>template-controller</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="inlineStr">
+        <is>
+          <t>/template/getRecommendation</t>
+        </is>
+      </c>
+      <c r="F134" s="3" t="n"/>
+      <c r="G134" s="3" t="n"/>
+    </row>
+    <row r="135" ht="16" customHeight="1">
+      <c r="A135" s="3" t="n"/>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C135" s="3" t="inlineStr">
+        <is>
+          <t>template-controller</t>
+        </is>
+      </c>
+      <c r="D135" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E135" s="3" t="inlineStr">
+        <is>
+          <t>/template/getTemplate</t>
+        </is>
+      </c>
+      <c r="F135" s="3" t="n"/>
+      <c r="G135" s="7" t="inlineStr">
+        <is>
+          <t>onlyFavorite:true查询收藏模板 — 47%</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="16" customHeight="1">
+      <c r="A136" s="3" t="n"/>
+      <c r="B136" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C136" s="3" t="inlineStr">
+        <is>
+          <t>template-controller</t>
+        </is>
+      </c>
+      <c r="D136" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="inlineStr">
+        <is>
+          <t>/template/getTemplateListFromDirectShare</t>
+        </is>
+      </c>
+      <c r="F136" s="3" t="n"/>
+      <c r="G136" s="7" t="inlineStr">
+        <is>
+          <t>通过直链分享获取模板列表</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="16" customHeight="1">
+      <c r="A137" s="3" t="n"/>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C137" s="3" t="inlineStr">
+        <is>
+          <t>template-controller</t>
+        </is>
+      </c>
+      <c r="D137" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="inlineStr">
+        <is>
+          <t>/template/getTemplateListFromSharePass</t>
+        </is>
+      </c>
+      <c r="F137" s="3" t="n"/>
+      <c r="G137" s="7" t="inlineStr">
+        <is>
+          <t>通过分享密码获取模板列表 — 0.09%</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="16" customHeight="1">
+      <c r="A138" s="3" t="n"/>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="inlineStr">
+        <is>
+          <t>template-controller</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E138" s="3" t="inlineStr">
+        <is>
+          <t>/template/moveDefaultTemplate</t>
+        </is>
+      </c>
+      <c r="F138" s="3" t="n"/>
+      <c r="G138" s="7" t="inlineStr">
+        <is>
+          <t>移动默认模板到分类</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="16" customHeight="1">
+      <c r="A139" s="3" t="n"/>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C139" s="3" t="inlineStr">
+        <is>
+          <t>template-controller</t>
+        </is>
+      </c>
+      <c r="D139" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E139" s="3" t="inlineStr">
+        <is>
+          <t>/template/moveTemplate</t>
+        </is>
+      </c>
+      <c r="F139" s="3" t="n"/>
+      <c r="G139" s="7" t="inlineStr">
+        <is>
+          <t>移动模板到分类(创建临时分类,可重复)</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="16" customHeight="1">
+      <c r="A140" s="3" t="n"/>
+      <c r="B140" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C140" s="3" t="inlineStr">
+        <is>
+          <t>to-event</t>
+        </is>
+      </c>
+      <c r="D140" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E140" s="3" t="inlineStr">
+        <is>
+          <t>/event/clearCacheTypes</t>
+        </is>
+      </c>
+      <c r="F140" s="3" t="n"/>
+      <c r="G140" s="7" t="inlineStr">
+        <is>
+          <t>清除规则缓存类型(无ES流量)（无ES流量）</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="16" customHeight="1">
+      <c r="A141" s="3" t="n"/>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C141" s="3" t="inlineStr">
+        <is>
+          <t>to-event</t>
+        </is>
+      </c>
+      <c r="D141" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="inlineStr">
+        <is>
+          <t>/event/getRuleCountByCampaignIds</t>
+        </is>
+      </c>
+      <c r="F141" s="3" t="n"/>
+      <c r="G141" s="7" t="inlineStr">
+        <is>
+          <t>按campaignId统计规则数量(无ES流量,TikTok返回405)（无ES流量）</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="16" customHeight="1">
+      <c r="A142" s="3" t="n"/>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr">
+        <is>
+          <t>to-event</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E142" s="3" t="inlineStr">
+        <is>
+          <t>/event/getRuleCountByUserIds</t>
+        </is>
+      </c>
+      <c r="F142" s="3" t="n"/>
+      <c r="G142" s="7" t="inlineStr">
+        <is>
+          <t>按userId统计TikTok规则数量 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="16" customHeight="1">
+      <c r="A143" s="3" t="n"/>
+      <c r="B143" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C143" s="3" t="inlineStr">
+        <is>
+          <t>to-event</t>
+        </is>
+      </c>
+      <c r="D143" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E143" s="3" t="inlineStr">
+        <is>
+          <t>/event/getRuleDefinition</t>
+        </is>
+      </c>
+      <c r="F143" s="3" t="n"/>
+      <c r="G143" s="7" t="inlineStr">
+        <is>
+          <t>按ruleIds批量获取规则定义(创建临时规则,可重复) — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="16" customHeight="1">
+      <c r="A144" s="3" t="n"/>
+      <c r="B144" s="3" t="inlineStr">
+        <is>
+          <t>amazon</t>
+        </is>
+      </c>
+      <c r="C144" s="3" t="inlineStr">
+        <is>
+          <t>to-event</t>
+        </is>
+      </c>
+      <c r="D144" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E144" s="3" t="inlineStr">
+        <is>
+          <t>/event/getRuleTypes</t>
+        </is>
+      </c>
+      <c r="F144" s="3" t="n"/>
+      <c r="G144" s="7" t="inlineStr">
+        <is>
+          <t>获取规则类型列表 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="16" customHeight="1">
+      <c r="A145" s="3" t="n"/>
+      <c r="B145" s="3" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="C145" s="3" t="inlineStr">
+        <is>
+          <t>auto-task-controller</t>
+        </is>
+      </c>
+      <c r="D145" s="3" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E145" s="3" t="inlineStr">
+        <is>
+          <t>/task/sendManualRuleMessage</t>
+        </is>
+      </c>
+      <c r="F145" s="3" t="n"/>
+      <c r="G145" s="7" t="inlineStr">
+        <is>
+          <t>手动触发规则消息（无ES流量）</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="16" customHeight="1">
+      <c r="A146" s="3" t="n"/>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="C146" s="3" t="inlineStr">
+        <is>
+          <t>config-controller</t>
+        </is>
+      </c>
+      <c r="D146" s="3" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E146" s="3" t="inlineStr">
+        <is>
+          <t>/config/actionMetrics</t>
+        </is>
+      </c>
+      <c r="F146" s="3" t="n"/>
+      <c r="G146" s="7" t="inlineStr">
+        <is>
+          <t>获取规则动作执行指标 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="16" customHeight="1">
+      <c r="A147" s="3" t="n"/>
+      <c r="B147" s="3" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="C147" s="3" t="inlineStr">
+        <is>
+          <t>config-controller</t>
+        </is>
+      </c>
+      <c r="D147" s="3" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E147" s="3" t="inlineStr">
+        <is>
+          <t>/config/emails</t>
+        </is>
+      </c>
+      <c r="F147" s="3" t="n"/>
+      <c r="G147" s="7" t="inlineStr">
+        <is>
+          <t>获取规则通知邮件列表 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="16" customHeight="1">
+      <c r="A148" s="3" t="n"/>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="C148" s="3" t="inlineStr">
+        <is>
+          <t>config-controller</t>
+        </is>
+      </c>
+      <c r="D148" s="3" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E148" s="3" t="inlineStr">
+        <is>
+          <t>/config/getAddOn</t>
+        </is>
+      </c>
+      <c r="F148" s="3" t="n"/>
+      <c r="G148" s="7" t="inlineStr">
+        <is>
+          <t>获取AddOn插件状态（无ES流量）</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="16" customHeight="1">
+      <c r="A149" s="3" t="n"/>
+      <c r="B149" s="3" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="C149" s="3" t="inlineStr">
+        <is>
+          <t>config-controller</t>
+        </is>
+      </c>
+      <c r="D149" s="3" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="inlineStr">
+        <is>
+          <t>/config/getCommercePermission</t>
+        </is>
+      </c>
+      <c r="F149" s="3" t="n"/>
+      <c r="G149" s="7" t="inlineStr">
+        <is>
+          <t>获取商业化功能权限 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="16" customHeight="1">
+      <c r="A150" s="3" t="n"/>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="C150" s="3" t="inlineStr">
+        <is>
+          <t>config-controller</t>
+        </is>
+      </c>
+      <c r="D150" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E150" s="3" t="inlineStr">
+        <is>
+          <t>/config/openAddOn</t>
+        </is>
+      </c>
+      <c r="F150" s="3" t="n"/>
+      <c r="G150" s="7" t="inlineStr">
+        <is>
+          <t>开通AddOn插件 [NEEDS REAL VALUE]（无ES流量）</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="16" customHeight="1">
+      <c r="A151" s="3" t="n"/>
+      <c r="B151" s="3" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="C151" s="3" t="inlineStr">
+        <is>
+          <t>config-controller</t>
+        </is>
+      </c>
+      <c r="D151" s="3" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E151" s="3" t="inlineStr">
+        <is>
+          <t>/config/requirementMetrics</t>
+        </is>
+      </c>
+      <c r="F151" s="3" t="n"/>
+      <c r="G151" s="7" t="inlineStr">
+        <is>
+          <t>获取规则条件指标配置 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="32" customHeight="1">
+      <c r="A152" s="3" t="n"/>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>config-controller</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E152" s="3" t="inlineStr">
+        <is>
+          <t>/config/RuleActionMetrics</t>
+        </is>
+      </c>
+      <c r="F152" s="3" t="n"/>
+      <c r="G152" s="7" t="inlineStr">
+        <is>
+          <t>获取规则动作指标配置 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="32" customHeight="1">
+      <c r="A153" s="3" t="n"/>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>config-controller</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E153" s="3" t="inlineStr">
+        <is>
+          <t>/config/RuleActionMetrics</t>
+        </is>
+      </c>
+      <c r="F153" s="3" t="n"/>
+      <c r="G153" s="7" t="inlineStr">
+        <is>
+          <t>保存自定义规则动作指标配置（无ES流量）</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="16" customHeight="1">
+      <c r="A154" s="3" t="n"/>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t>config-controller</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E154" s="3" t="inlineStr">
+        <is>
+          <t>/config/ruleTypes</t>
+        </is>
+      </c>
+      <c r="F154" s="3" t="n"/>
+      <c r="G154" s="7" t="inlineStr">
+        <is>
+          <t>获取规则类型枚举列表 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="16" customHeight="1">
+      <c r="A155" s="3" t="n"/>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>config-controller</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E155" s="3" t="inlineStr">
+        <is>
+          <t>/config/supportedTimeZones</t>
+        </is>
+      </c>
+      <c r="F155" s="3" t="n"/>
+      <c r="G155" s="7" t="inlineStr">
+        <is>
+          <t>获取支持的时区列表 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="16" customHeight="1">
+      <c r="A156" s="3" t="n"/>
+      <c r="B156" s="3" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="C156" s="3" t="inlineStr">
+        <is>
+          <t>data-impact-controller</t>
+        </is>
+      </c>
+      <c r="D156" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E156" s="3" t="inlineStr">
+        <is>
+          <t>/dataImpact/brandOrManufacturers</t>
+        </is>
+      </c>
+      <c r="F156" s="3" t="n"/>
+      <c r="G156" s="7" t="inlineStr">
+        <is>
+          <t>查询品牌/制造商数据（无ES流量）</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="16" customHeight="1">
+      <c r="A157" s="3" t="n"/>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="C157" s="3" t="inlineStr">
+        <is>
+          <t>data-impact-controller</t>
+        </is>
+      </c>
+      <c r="D157" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E157" s="3" t="inlineStr">
+        <is>
+          <t>/dataImpact/categories</t>
+        </is>
+      </c>
+      <c r="F157" s="3" t="n"/>
+      <c r="G157" s="7" t="inlineStr">
+        <is>
+          <t>查询数据影响分类（无ES流量）</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="16" customHeight="1">
+      <c r="A158" s="3" t="n"/>
+      <c r="B158" s="3" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="C158" s="3" t="inlineStr">
+        <is>
+          <t>data-impact-controller</t>
+        </is>
+      </c>
+      <c r="D158" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E158" s="3" t="inlineStr">
+        <is>
+          <t>/dataImpact/oos/asinList</t>
+        </is>
+      </c>
+      <c r="F158" s="3" t="n"/>
+      <c r="G158" s="7" t="inlineStr">
+        <is>
+          <t>查询OOS ASIN列表 — 1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="16" customHeight="1">
+      <c r="A159" s="3" t="n"/>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="inlineStr">
+        <is>
+          <t>data-impact-controller</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E159" s="3" t="inlineStr">
+        <is>
+          <t>/dataImpact/oos/brandList</t>
+        </is>
+      </c>
+      <c r="F159" s="3" t="n"/>
+      <c r="G159" s="7" t="inlineStr">
+        <is>
+          <t>查询OOS品牌列表 — 2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="16" customHeight="1">
+      <c r="A160" s="3" t="n"/>
+      <c r="B160" s="3" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="C160" s="3" t="inlineStr">
+        <is>
+          <t>data-impact-controller</t>
+        </is>
+      </c>
+      <c r="D160" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E160" s="3" t="inlineStr">
+        <is>
+          <t>/dataImpact/price/asinList</t>
+        </is>
+      </c>
+      <c r="F160" s="3" t="n"/>
+      <c r="G160" s="7" t="inlineStr">
+        <is>
+          <t>查询价格ASIN列表 — 2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="3" t="n"/>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="C161" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="D161" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E161" s="3" t="inlineStr">
+        <is>
+          <t>/automationPauseAsins</t>
+        </is>
+      </c>
+      <c r="F161" s="3" t="n"/>
+      <c r="G161" s="8" t="inlineStr">
+        <is>
+          <t>TikTok 平台无生产流量，暂不生成 case</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="16" customHeight="1">
+      <c r="A162" s="3" t="n"/>
+      <c r="B162" s="3" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="C162" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="D162" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E162" s="3" t="inlineStr">
+        <is>
+          <t>/bulk-create/tiktok/roas-explorer</t>
+        </is>
+      </c>
+      <c r="F162" s="3" t="n"/>
+      <c r="G162" s="7" t="inlineStr">
+        <is>
+          <t>批量创建TikTok RoasExplorer规则(含后置删除,可重复) — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="3" t="n"/>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="D163" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E163" s="3" t="inlineStr">
+        <is>
+          <t>/bulk-create/tiktok/smart-budget-boost</t>
+        </is>
+      </c>
+      <c r="F163" s="3" t="n"/>
+      <c r="G163" s="8" t="inlineStr">
+        <is>
+          <t>TikTok 平台无生产流量，暂不生成 case</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="3" t="n"/>
+      <c r="B164" s="3" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="C164" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="D164" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E164" s="3" t="inlineStr">
+        <is>
+          <t>/bulkCreateRule</t>
+        </is>
+      </c>
+      <c r="F164" s="3" t="n"/>
+      <c r="G164" s="8" t="inlineStr">
+        <is>
+          <t>TikTok 平台无生产流量，暂不生成 case</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="3" t="n"/>
+      <c r="B165" s="3" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="C165" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="D165" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E165" s="3" t="inlineStr">
+        <is>
+          <t>/createAdtomicRule</t>
+        </is>
+      </c>
+      <c r="F165" s="3" t="n"/>
+      <c r="G165" s="8" t="inlineStr">
+        <is>
+          <t>TikTok 平台无生产流量，暂不生成 case</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="16" customHeight="1">
+      <c r="A166" s="3" t="n"/>
+      <c r="B166" s="3" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="D166" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E166" s="3" t="inlineStr">
+        <is>
+          <t>/definition</t>
+        </is>
+      </c>
+      <c r="F166" s="3" t="n"/>
+      <c r="G166" s="7" t="inlineStr">
+        <is>
+          <t>创建TikTok BudgetBoost规则(含后置删除,可重复) — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="16" customHeight="1">
+      <c r="A167" s="3" t="n"/>
+      <c r="B167" s="3" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="C167" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="D167" s="3" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E167" s="3" t="inlineStr">
+        <is>
+          <t>/definition/{ruleId}</t>
+        </is>
+      </c>
+      <c r="F167" s="3" t="n"/>
+      <c r="G167" s="3" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="3" t="n"/>
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="C168" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="D168" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E168" s="3" t="inlineStr">
+        <is>
+          <t>/definition/addAppliedObj</t>
+        </is>
+      </c>
+      <c r="F168" s="3" t="n"/>
+      <c r="G168" s="8" t="inlineStr">
+        <is>
+          <t>TikTok 平台无生产流量，暂不生成 case</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="3" t="n"/>
+      <c r="B169" s="3" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="C169" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="D169" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E169" s="3" t="inlineStr">
+        <is>
+          <t>/definition/addAppliedObjBySeparateRule</t>
+        </is>
+      </c>
+      <c r="F169" s="3" t="n"/>
+      <c r="G169" s="8" t="inlineStr">
+        <is>
+          <t>TikTok 平台无生产流量，暂不生成 case</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="3" t="n"/>
+      <c r="B170" s="3" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="C170" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="D170" s="3" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E170" s="3" t="inlineStr">
+        <is>
+          <t>/definition/adtomic/{adtomicRuleId}</t>
+        </is>
+      </c>
+      <c r="F170" s="3" t="n"/>
+      <c r="G170" s="8" t="inlineStr">
+        <is>
+          <t>TikTok 平台无生产流量，暂不生成 case</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="16" customHeight="1">
+      <c r="A171" s="3" t="n"/>
+      <c r="B171" s="3" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="C171" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="D171" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E171" s="3" t="inlineStr">
+        <is>
+          <t>/definition/adtomicRules/settings</t>
+        </is>
+      </c>
+      <c r="F171" s="3" t="n"/>
+      <c r="G171" s="8" t="inlineStr">
+        <is>
+          <t>TikTok 平台无生产流量，暂不生成 case</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="3" t="n"/>
+      <c r="B172" s="3" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="C172" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="D172" s="3" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E172" s="3" t="inlineStr">
+        <is>
+          <t>/definition/adtomicRules/settings/{profileId}</t>
+        </is>
+      </c>
+      <c r="F172" s="3" t="n"/>
+      <c r="G172" s="8" t="inlineStr">
+        <is>
+          <t>TikTok 平台无生产流量，暂不生成 case</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="3" t="n"/>
+      <c r="B173" s="3" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="C173" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="D173" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E173" s="3" t="inlineStr">
+        <is>
+          <t>/definition/calculateNextExecutionTime</t>
+        </is>
+      </c>
+      <c r="F173" s="3" t="n"/>
+      <c r="G173" s="8" t="inlineStr">
+        <is>
+          <t>TikTok 平台无生产流量，暂不生成 case</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="3" t="n"/>
+      <c r="B174" s="3" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="C174" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="D174" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E174" s="3" t="inlineStr">
+        <is>
+          <t>/definition/changeOwners</t>
+        </is>
+      </c>
+      <c r="F174" s="3" t="n"/>
+      <c r="G174" s="8" t="inlineStr">
+        <is>
+          <t>TikTok 平台无生产流量，暂不生成 case</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="16" customHeight="1">
+      <c r="A175" s="3" t="n"/>
+      <c r="B175" s="3" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="C175" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="D175" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E175" s="3" t="inlineStr">
+        <is>
+          <t>/definition/changeStatus</t>
+        </is>
+      </c>
+      <c r="F175" s="3" t="n"/>
+      <c r="G175" s="7" t="inlineStr">
+        <is>
+          <t>暂停/恢复规则(创建临时规则,可重复) — 40%</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="3" t="n"/>
+      <c r="B176" s="3" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="C176" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="D176" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E176" s="3" t="inlineStr">
+        <is>
+          <t>/definition/checkAutoRefillRule</t>
+        </is>
+      </c>
+      <c r="F176" s="3" t="n"/>
+      <c r="G176" s="8" t="inlineStr">
+        <is>
+          <t>TikTok 平台无生产流量，暂不生成 case</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="3" t="n"/>
+      <c r="B177" s="3" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="C177" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="D177" s="3" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E177" s="3" t="inlineStr">
+        <is>
+          <t>/definition/checkCustom/{ruleId}</t>
+        </is>
+      </c>
+      <c r="F177" s="3" t="n"/>
+      <c r="G177" s="8" t="inlineStr">
+        <is>
+          <t>TikTok 平台无生产流量，暂不生成 case</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="32" customHeight="1">
+      <c r="A178" s="3" t="n"/>
+      <c r="B178" s="3" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="C178" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="D178" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E178" s="3" t="inlineStr">
+        <is>
+          <t>/definition/checkRuleName</t>
+        </is>
+      </c>
+      <c r="F178" s="3" t="n"/>
+      <c r="G178" s="7" t="inlineStr">
+        <is>
+          <t>新建规则名称重复校验 — 80%
+编辑规则名称重复校验(创建临时规则,可重复) — 20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="3" t="n"/>
+      <c r="B179" s="3" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="C179" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="D179" s="3" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E179" s="3" t="inlineStr">
+        <is>
+          <t>/definition/commerceRuleClient</t>
+        </is>
+      </c>
+      <c r="F179" s="3" t="n"/>
+      <c r="G179" s="8" t="inlineStr">
+        <is>
+          <t>TikTok 平台无生产流量，暂不生成 case</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="16" customHeight="1">
+      <c r="A180" s="3" t="n"/>
+      <c r="B180" s="3" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="C180" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="D180" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E180" s="3" t="inlineStr">
+        <is>
+          <t>/definition/commerceRuleReport</t>
+        </is>
+      </c>
+      <c r="F180" s="3" t="n"/>
+      <c r="G180" s="8" t="inlineStr">
+        <is>
+          <t>TikTok 平台无生产流量，暂不生成 case</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="3" t="n"/>
+      <c r="B181" s="3" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="C181" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="D181" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E181" s="3" t="inlineStr">
+        <is>
+          <t>/definition/delete/{adtomicRuleId}</t>
+        </is>
+      </c>
+      <c r="F181" s="3" t="n"/>
+      <c r="G181" s="8" t="inlineStr">
+        <is>
+          <t>TikTok 平台无生产流量，暂不生成 case</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="3" t="n"/>
+      <c r="B182" s="3" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="C182" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="D182" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E182" s="3" t="inlineStr">
+        <is>
+          <t>/definition/editAdtomicRule</t>
+        </is>
+      </c>
+      <c r="F182" s="3" t="n"/>
+      <c r="G182" s="8" t="inlineStr">
+        <is>
+          <t>TikTok 平台无生产流量，暂不生成 case</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="32" customHeight="1">
+      <c r="A183" s="3" t="n"/>
+      <c r="B183" s="3" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="C183" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="D183" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E183" s="3" t="inlineStr">
+        <is>
+          <t>/definition/editRule</t>
+        </is>
+      </c>
+      <c r="F183" s="3" t="n"/>
+      <c r="G183" s="7" t="inlineStr">
+        <is>
+          <t>编辑TikTok Campaign级规则(创建临时规则,可重复) — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="3" t="n"/>
+      <c r="B184" s="3" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="C184" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="D184" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E184" s="3" t="inlineStr">
+        <is>
+          <t>/definition/export</t>
+        </is>
+      </c>
+      <c r="F184" s="3" t="n"/>
+      <c r="G184" s="8" t="inlineStr">
+        <is>
+          <t>TikTok 平台无生产流量，暂不生成 case</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="3" t="n"/>
+      <c r="B185" s="3" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="C185" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="D185" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E185" s="3" t="inlineStr">
+        <is>
+          <t>/definition/export/commerceRuleReport</t>
+        </is>
+      </c>
+      <c r="F185" s="3" t="n"/>
+      <c r="G185" s="8" t="inlineStr">
+        <is>
+          <t>TikTok 平台无生产流量，暂不生成 case</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="3" t="n"/>
+      <c r="B186" s="3" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="C186" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="D186" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E186" s="3" t="inlineStr">
+        <is>
+          <t>/definition/getAdtomicRules</t>
+        </is>
+      </c>
+      <c r="F186" s="3" t="n"/>
+      <c r="G186" s="8" t="inlineStr">
+        <is>
+          <t>TikTok 平台无生产流量，暂不生成 case</t>
+        </is>
+      </c>
+    </row>
+    <row r="187" ht="16" customHeight="1">
+      <c r="A187" s="3" t="n"/>
+      <c r="B187" s="3" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="C187" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="D187" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E187" s="3" t="inlineStr">
+        <is>
+          <t>/definition/getApplyRule</t>
+        </is>
+      </c>
+      <c r="F187" s="3" t="n"/>
+      <c r="G187" s="7" t="inlineStr">
+        <is>
+          <t>查询规则应用列表 — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="16" customHeight="1">
+      <c r="A188" s="3" t="n"/>
+      <c r="B188" s="3" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="C188" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="D188" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E188" s="3" t="inlineStr">
+        <is>
+          <t>/definition/getAsinRelatedRule</t>
+        </is>
+      </c>
+      <c r="F188" s="3" t="n"/>
+      <c r="G188" s="8" t="inlineStr">
+        <is>
+          <t>TikTok 平台无生产流量，暂不生成 case</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="3" t="n"/>
+      <c r="B189" s="3" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="C189" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="D189" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E189" s="3" t="inlineStr">
+        <is>
+          <t>/definition/getAutoRefillRuleApplyTagCampaigns</t>
+        </is>
+      </c>
+      <c r="F189" s="3" t="n"/>
+      <c r="G189" s="8" t="inlineStr">
+        <is>
+          <t>TikTok 平台无生产流量，暂不生成 case</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="3" t="n"/>
+      <c r="B190" s="3" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="C190" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="D190" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E190" s="3" t="inlineStr">
+        <is>
+          <t>/definition/getAutoRefillRuleApplyTags</t>
+        </is>
+      </c>
+      <c r="F190" s="3" t="n"/>
+      <c r="G190" s="8" t="inlineStr">
+        <is>
+          <t>TikTok 平台无生产流量，暂不生成 case</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="3" t="n"/>
+      <c r="B191" s="3" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="C191" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="D191" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E191" s="3" t="inlineStr">
+        <is>
+          <t>/definition/getAutoRefillRuleApplyTargets</t>
+        </is>
+      </c>
+      <c r="F191" s="3" t="n"/>
+      <c r="G191" s="8" t="inlineStr">
+        <is>
+          <t>TikTok 平台无生产流量，暂不生成 case</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="16" customHeight="1">
+      <c r="A192" s="3" t="n"/>
+      <c r="B192" s="3" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="C192" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="D192" s="3" t="inlineStr">
+        <is>
+          <t>GET</t>
+        </is>
+      </c>
+      <c r="E192" s="3" t="inlineStr">
+        <is>
+          <t>/definition/getAutoRefillRuleProfileIds</t>
+        </is>
+      </c>
+      <c r="F192" s="3" t="n"/>
+      <c r="G192" s="7" t="inlineStr">
+        <is>
+          <t>查询AutoRefill规则关联profile — 100%</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="3" t="n"/>
+      <c r="B193" s="3" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="C193" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="D193" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E193" s="3" t="inlineStr">
+        <is>
+          <t>/definition/getCampaignWithRule</t>
+        </is>
+      </c>
+      <c r="F193" s="3" t="n"/>
+      <c r="G193" s="8" t="inlineStr">
+        <is>
+          <t>TikTok 平台无生产流量，暂不生成 case</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="48" customHeight="1">
+      <c r="A194" s="3" t="n"/>
+      <c r="B194" s="3" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="C194" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="D194" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E194" s="3" t="inlineStr">
+        <is>
+          <t>/definition/getOwners</t>
+        </is>
+      </c>
+      <c r="F194" s="3" t="n"/>
+      <c r="G194" s="7" t="inlineStr">
+        <is>
           <t>Auto模式获取规则负责人 — 42%
 Manual模式获取规则负责人 — 30%
 AutoCommerce模式获取规则负责人 — 20%</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="3" t="n"/>
-      <c r="B50" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D50" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="inlineStr">
+    <row r="195">
+      <c r="A195" s="3" t="n"/>
+      <c r="B195" s="3" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="C195" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="D195" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E195" s="3" t="inlineStr">
         <is>
           <t>/definition/getProfile</t>
         </is>
       </c>
-      <c r="F50" s="3" t="n"/>
-      <c r="G50" s="3" t="n"/>
-    </row>
-    <row r="51" ht="48" customHeight="1">
-      <c r="A51" s="3" t="n"/>
-      <c r="B51" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D51" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="inlineStr">
+      <c r="F195" s="3" t="n"/>
+      <c r="G195" s="8" t="inlineStr">
+        <is>
+          <t>TikTok 平台无生产流量，暂不生成 case</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="48" customHeight="1">
+      <c r="A196" s="3" t="n"/>
+      <c r="B196" s="3" t="inlineStr">
+        <is>
+          <t>tiktok</t>
+        </is>
+      </c>
+      <c r="C196" s="3" t="inlineStr">
+        <is>
+          <t>definition-controller</t>
+        </is>
+      </c>
+      <c r="D196" s="3" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="E196" s="3" t="inlineStr">
         <is>
           <t>/definition/getRule</t>
         </is>
       </c>
-      <c r="F51" s="3" t="n"/>
-      <c r="G51" s="7" t="inlineStr">
+      <c r="F196" s="3" t="n"/>
+      <c r="G196" s="7" t="inlineStr">
         <is>
           <t>Auto模式默认规则列表 — 53%
 按ruleIds精确查询(创建临时规则,可重复) — 22%
@@ -5435,4149 +9735,6 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="3" t="n"/>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D52" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E52" s="3" t="inlineStr">
-        <is>
-          <t>/definition/getRuleInfoByCampaignId</t>
-        </is>
-      </c>
-      <c r="F52" s="3" t="n"/>
-      <c r="G52" s="3" t="n"/>
-    </row>
-    <row r="53" ht="48" customHeight="1">
-      <c r="A53" s="3" t="n"/>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="inlineStr">
-        <is>
-          <t>/definition/getRuleTargetInfo</t>
-        </is>
-      </c>
-      <c r="F53" s="3" t="n"/>
-      <c r="G53" s="3" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="n"/>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D54" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E54" s="3" t="inlineStr">
-        <is>
-          <t>/definition/getRuleTargetInfoByRuleIds</t>
-        </is>
-      </c>
-      <c r="F54" s="3" t="n"/>
-      <c r="G54" s="3" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="3" t="n"/>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C55" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D55" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E55" s="3" t="inlineStr">
-        <is>
-          <t>/definition/getTarget</t>
-        </is>
-      </c>
-      <c r="F55" s="3" t="n"/>
-      <c r="G55" s="3" t="n"/>
-    </row>
-    <row r="56" ht="16" customHeight="1">
-      <c r="A56" s="3" t="n"/>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C56" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D56" s="3" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="inlineStr">
-        <is>
-          <t>/definition/hasClickHitMode</t>
-        </is>
-      </c>
-      <c r="F56" s="3" t="n"/>
-      <c r="G56" s="7" t="inlineStr">
-        <is>
-          <t>查询是否支持ClickHit模式 — 100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="16" customHeight="1">
-      <c r="A57" s="3" t="n"/>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="E57" s="3" t="inlineStr">
-        <is>
-          <t>/definition/transferableOwnerList</t>
-        </is>
-      </c>
-      <c r="F57" s="3" t="n"/>
-      <c r="G57" s="7" t="inlineStr">
-        <is>
-          <t>查询可转移规则的负责人列表 — 100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="16" customHeight="1">
-      <c r="A58" s="3" t="n"/>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D58" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E58" s="3" t="inlineStr">
-        <is>
-          <t>/definition/updateAppliedObj</t>
-        </is>
-      </c>
-      <c r="F58" s="3" t="n"/>
-      <c r="G58" s="7" t="inlineStr">
-        <is>
-          <t>更新规则应用对象(创建临时规则,可重复) — 100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="16" customHeight="1">
-      <c r="A59" s="3" t="n"/>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C59" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D59" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E59" s="3" t="inlineStr">
-        <is>
-          <t>/definition/updateAutomation</t>
-        </is>
-      </c>
-      <c r="F59" s="3" t="n"/>
-      <c r="G59" s="3" t="n"/>
-    </row>
-    <row r="60" ht="16" customHeight="1">
-      <c r="A60" s="3" t="n"/>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C60" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D60" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E60" s="3" t="inlineStr">
-        <is>
-          <t>/downloadMapping</t>
-        </is>
-      </c>
-      <c r="F60" s="3" t="n"/>
-      <c r="G60" s="3" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="3" t="n"/>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D61" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E61" s="3" t="inlineStr">
-        <is>
-          <t>/downloadMapping/{id}</t>
-        </is>
-      </c>
-      <c r="F61" s="3" t="n"/>
-      <c r="G61" s="3" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="3" t="n"/>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D62" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="inlineStr">
-        <is>
-          <t>/getRuleViewList</t>
-        </is>
-      </c>
-      <c r="F62" s="3" t="n"/>
-      <c r="G62" s="3" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="n"/>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D63" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="inlineStr">
-        <is>
-          <t>/terminatedClientRule</t>
-        </is>
-      </c>
-      <c r="F63" s="3" t="n"/>
-      <c r="G63" s="3" t="n"/>
-    </row>
-    <row r="64" ht="16" customHeight="1">
-      <c r="A64" s="3" t="n"/>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t>feature-usage-controller</t>
-        </is>
-      </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="inlineStr">
-        <is>
-          <t>/featureHealth/monthlyReport</t>
-        </is>
-      </c>
-      <c r="F64" s="3" t="n"/>
-      <c r="G64" s="7" t="inlineStr">
-        <is>
-          <t>walmart平台月度功能使用报告 — 2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="16" customHeight="1">
-      <c r="A65" s="3" t="n"/>
-      <c r="B65" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C65" s="3" t="inlineStr">
-        <is>
-          <t>feature-usage-controller</t>
-        </is>
-      </c>
-      <c r="D65" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E65" s="3" t="inlineStr">
-        <is>
-          <t>/featureHealth/topNClients</t>
-        </is>
-      </c>
-      <c r="F65" s="3" t="n"/>
-      <c r="G65" s="7" t="inlineStr">
-        <is>
-          <t>amazon平台Top N客户功能使用排行 — 2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="32" customHeight="1">
-      <c r="A66" s="3" t="n"/>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C66" s="3" t="inlineStr">
-        <is>
-          <t>health-controller</t>
-        </is>
-      </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="inlineStr">
-        <is>
-          <t>/health</t>
-        </is>
-      </c>
-      <c r="F66" s="3" t="n"/>
-      <c r="G66" s="7" t="inlineStr">
-        <is>
-          <t>服务健康检查（无ES流量）</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="16" customHeight="1">
-      <c r="A67" s="3" t="n"/>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C67" s="3" t="inlineStr">
-        <is>
-          <t>history-controller</t>
-        </is>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E67" s="3" t="inlineStr">
-        <is>
-          <t>/changeSuggestionStatus</t>
-        </is>
-      </c>
-      <c r="F67" s="3" t="n"/>
-      <c r="G67" s="7" t="inlineStr">
-        <is>
-          <t>变更建议操作状态[需实际建议记录]（无ES流量）</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="16" customHeight="1">
-      <c r="A68" s="3" t="n"/>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="inlineStr">
-        <is>
-          <t>history-controller</t>
-        </is>
-      </c>
-      <c r="D68" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E68" s="3" t="inlineStr">
-        <is>
-          <t>/getAdGroups/{ruleExecutionLogId}</t>
-        </is>
-      </c>
-      <c r="F68" s="3" t="n"/>
-      <c r="G68" s="7" t="inlineStr">
-        <is>
-          <t>执行日志AdGroup列表（无ES流量）</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="16" customHeight="1">
-      <c r="A69" s="3" t="n"/>
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="inlineStr">
-        <is>
-          <t>history-controller</t>
-        </is>
-      </c>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="inlineStr">
-        <is>
-          <t>/getAdtomicSuggestions</t>
-        </is>
-      </c>
-      <c r="F69" s="3" t="n"/>
-      <c r="G69" s="7" t="inlineStr">
-        <is>
-          <t>Adtomic建议操作列表（无ES流量）</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="16" customHeight="1">
-      <c r="A70" s="3" t="n"/>
-      <c r="B70" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C70" s="3" t="inlineStr">
-        <is>
-          <t>history-controller</t>
-        </is>
-      </c>
-      <c r="D70" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E70" s="3" t="inlineStr">
-        <is>
-          <t>/getAutoRuleDetailLog</t>
-        </is>
-      </c>
-      <c r="F70" s="3" t="n"/>
-      <c r="G70" s="7" t="inlineStr">
-        <is>
-          <t>自动规则详情日志[Amazon专属]（无ES流量）</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="16" customHeight="1">
-      <c r="A71" s="3" t="n"/>
-      <c r="B71" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C71" s="3" t="inlineStr">
-        <is>
-          <t>history-controller</t>
-        </is>
-      </c>
-      <c r="D71" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E71" s="3" t="inlineStr">
-        <is>
-          <t>/getAutoRuleDetailLogFilter</t>
-        </is>
-      </c>
-      <c r="F71" s="3" t="n"/>
-      <c r="G71" s="7" t="inlineStr">
-        <is>
-          <t>自动规则日志过滤器[Amazon专属]（无ES流量）</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="16" customHeight="1">
-      <c r="A72" s="3" t="n"/>
-      <c r="B72" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C72" s="3" t="inlineStr">
-        <is>
-          <t>history-controller</t>
-        </is>
-      </c>
-      <c r="D72" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E72" s="3" t="inlineStr">
-        <is>
-          <t>/getAutoRuleLogList</t>
-        </is>
-      </c>
-      <c r="F72" s="3" t="n"/>
-      <c r="G72" s="7" t="inlineStr">
-        <is>
-          <t>自动规则执行日志列表[Amazon专属]（无ES流量）</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="16" customHeight="1">
-      <c r="A73" s="3" t="n"/>
-      <c r="B73" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C73" s="3" t="inlineStr">
-        <is>
-          <t>history-controller</t>
-        </is>
-      </c>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E73" s="3" t="inlineStr">
-        <is>
-          <t>/getCampaigns/{ruleExecutionLogId}</t>
-        </is>
-      </c>
-      <c r="F73" s="3" t="n"/>
-      <c r="G73" s="7" t="inlineStr">
-        <is>
-          <t>执行日志Campaign列表 — 100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="16" customHeight="1">
-      <c r="A74" s="3" t="n"/>
-      <c r="B74" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C74" s="3" t="inlineStr">
-        <is>
-          <t>history-controller</t>
-        </is>
-      </c>
-      <c r="D74" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E74" s="3" t="inlineStr">
-        <is>
-          <t>/getCampaignTags/{ruleExecutionLogId}</t>
-        </is>
-      </c>
-      <c r="F74" s="3" t="n"/>
-      <c r="G74" s="7" t="inlineStr">
-        <is>
-          <t>执行日志CampaignTag列表 — 100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="16" customHeight="1">
-      <c r="A75" s="3" t="n"/>
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C75" s="3" t="inlineStr">
-        <is>
-          <t>history-controller</t>
-        </is>
-      </c>
-      <c r="D75" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E75" s="3" t="inlineStr">
-        <is>
-          <t>/getDetail/{ruleExecutionLogId}</t>
-        </is>
-      </c>
-      <c r="F75" s="3" t="n"/>
-      <c r="G75" s="7" t="inlineStr">
-        <is>
-          <t>执行日志详情[需TikTok执行历史]（无ES流量）</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="16" customHeight="1">
-      <c r="A76" s="3" t="n"/>
-      <c r="B76" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C76" s="3" t="inlineStr">
-        <is>
-          <t>history-controller</t>
-        </is>
-      </c>
-      <c r="D76" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E76" s="3" t="inlineStr">
-        <is>
-          <t>/getHistoryList</t>
-        </is>
-      </c>
-      <c r="F76" s="3" t="n"/>
-      <c r="G76" s="7" t="inlineStr">
-        <is>
-          <t>历史执行记录列表 — 100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="16" customHeight="1">
-      <c r="A77" s="3" t="n"/>
-      <c r="B77" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C77" s="3" t="inlineStr">
-        <is>
-          <t>history-controller</t>
-        </is>
-      </c>
-      <c r="D77" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E77" s="3" t="inlineStr">
-        <is>
-          <t>/getLineItems/{ruleExecutionLogId}</t>
-        </is>
-      </c>
-      <c r="F77" s="3" t="n"/>
-      <c r="G77" s="7" t="inlineStr">
-        <is>
-          <t>执行日志LineItem列表（无ES流量）</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="16" customHeight="1">
-      <c r="A78" s="3" t="n"/>
-      <c r="B78" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C78" s="3" t="inlineStr">
-        <is>
-          <t>history-controller</t>
-        </is>
-      </c>
-      <c r="D78" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E78" s="3" t="inlineStr">
-        <is>
-          <t>/getPendingList</t>
-        </is>
-      </c>
-      <c r="F78" s="3" t="n"/>
-      <c r="G78" s="7" t="inlineStr">
-        <is>
-          <t>待处理规则列表 — 100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="16" customHeight="1">
-      <c r="A79" s="3" t="n"/>
-      <c r="B79" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C79" s="3" t="inlineStr">
-        <is>
-          <t>history-controller</t>
-        </is>
-      </c>
-      <c r="D79" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E79" s="3" t="inlineStr">
-        <is>
-          <t>/getPendingRuleNum</t>
-        </is>
-      </c>
-      <c r="F79" s="3" t="n"/>
-      <c r="G79" s="7" t="inlineStr">
-        <is>
-          <t>待处理规则数量 — 100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="16" customHeight="1">
-      <c r="A80" s="3" t="n"/>
-      <c r="B80" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C80" s="3" t="inlineStr">
-        <is>
-          <t>history-controller</t>
-        </is>
-      </c>
-      <c r="D80" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E80" s="3" t="inlineStr">
-        <is>
-          <t>/getProducts/{ruleExecutionLogId}</t>
-        </is>
-      </c>
-      <c r="F80" s="3" t="n"/>
-      <c r="G80" s="7" t="inlineStr">
-        <is>
-          <t>执行日志Product列表（无ES流量）</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="16" customHeight="1">
-      <c r="A81" s="3" t="n"/>
-      <c r="B81" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C81" s="3" t="inlineStr">
-        <is>
-          <t>history-controller</t>
-        </is>
-      </c>
-      <c r="D81" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E81" s="3" t="inlineStr">
-        <is>
-          <t>/getProfiles</t>
-        </is>
-      </c>
-      <c r="F81" s="3" t="n"/>
-      <c r="G81" s="7" t="inlineStr">
-        <is>
-          <t>执行日志Profile列表 — 100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="16" customHeight="1">
-      <c r="A82" s="3" t="n"/>
-      <c r="B82" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C82" s="3" t="inlineStr">
-        <is>
-          <t>history-controller</t>
-        </is>
-      </c>
-      <c r="D82" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E82" s="3" t="inlineStr">
-        <is>
-          <t>/history/archiveOldLogsTask</t>
-        </is>
-      </c>
-      <c r="F82" s="3" t="n"/>
-      <c r="G82" s="7" t="inlineStr">
-        <is>
-          <t>归档旧日志（运维接口）（无ES流量）</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="16" customHeight="1">
-      <c r="A83" s="3" t="n"/>
-      <c r="B83" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C83" s="3" t="inlineStr">
-        <is>
-          <t>history-controller</t>
-        </is>
-      </c>
-      <c r="D83" s="3" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="E83" s="3" t="inlineStr">
-        <is>
-          <t>/history/deleteHistoryData/{tableName}</t>
-        </is>
-      </c>
-      <c r="F83" s="3" t="n"/>
-      <c r="G83" s="7" t="inlineStr">
-        <is>
-          <t>清理历史数据（运维接口） — 100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="16" customHeight="1">
-      <c r="A84" s="3" t="n"/>
-      <c r="B84" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C84" s="3" t="inlineStr">
-        <is>
-          <t>history-controller</t>
-        </is>
-      </c>
-      <c r="D84" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E84" s="3" t="inlineStr">
-        <is>
-          <t>/history/export/{ruleExecutionLogId}</t>
-        </is>
-      </c>
-      <c r="F84" s="3" t="n"/>
-      <c r="G84" s="7" t="inlineStr">
-        <is>
-          <t>导出执行日志[需TikTok执行历史]（无ES流量）</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="16" customHeight="1">
-      <c r="A85" s="3" t="n"/>
-      <c r="B85" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C85" s="3" t="inlineStr">
-        <is>
-          <t>history-controller</t>
-        </is>
-      </c>
-      <c r="D85" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E85" s="3" t="inlineStr">
-        <is>
-          <t>/history/getLastPauseAsins/{ruleId}</t>
-        </is>
-      </c>
-      <c r="F85" s="3" t="n"/>
-      <c r="G85" s="7" t="inlineStr">
-        <is>
-          <t>规则最近暂停ASIN列表（无ES流量）</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="16" customHeight="1">
-      <c r="A86" s="3" t="n"/>
-      <c r="B86" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C86" s="3" t="inlineStr">
-        <is>
-          <t>history-controller</t>
-        </is>
-      </c>
-      <c r="D86" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E86" s="3" t="inlineStr">
-        <is>
-          <t>/history/getRuleAlertCount</t>
-        </is>
-      </c>
-      <c r="F86" s="3" t="n"/>
-      <c r="G86" s="7" t="inlineStr">
-        <is>
-          <t>标准告警计数查询 — 100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="16" customHeight="1">
-      <c r="A87" s="3" t="n"/>
-      <c r="B87" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C87" s="3" t="inlineStr">
-        <is>
-          <t>history-controller</t>
-        </is>
-      </c>
-      <c r="D87" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E87" s="3" t="inlineStr">
-        <is>
-          <t>/history/getRuleAlertDetail</t>
-        </is>
-      </c>
-      <c r="F87" s="3" t="n"/>
-      <c r="G87" s="7" t="inlineStr">
-        <is>
-          <t>规则告警详情列表 — 100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="88" ht="16" customHeight="1">
-      <c r="A88" s="3" t="n"/>
-      <c r="B88" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C88" s="3" t="inlineStr">
-        <is>
-          <t>history-controller</t>
-        </is>
-      </c>
-      <c r="D88" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E88" s="3" t="inlineStr">
-        <is>
-          <t>/history/getRuleDeadDetail</t>
-        </is>
-      </c>
-      <c r="F88" s="3" t="n"/>
-      <c r="G88" s="7" t="inlineStr">
-        <is>
-          <t>规则失效详情（无ES流量）</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="16" customHeight="1">
-      <c r="A89" s="3" t="n"/>
-      <c r="B89" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C89" s="3" t="inlineStr">
-        <is>
-          <t>history-controller</t>
-        </is>
-      </c>
-      <c r="D89" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E89" s="3" t="inlineStr">
-        <is>
-          <t>/pending/export/{ruleExecutionLogId}</t>
-        </is>
-      </c>
-      <c r="F89" s="3" t="n"/>
-      <c r="G89" s="7" t="inlineStr">
-        <is>
-          <t>导出待处理列表[需TikTok执行历史]（无ES流量）</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="16" customHeight="1">
-      <c r="A90" s="3" t="n"/>
-      <c r="B90" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C90" s="3" t="inlineStr">
-        <is>
-          <t>history-controller</t>
-        </is>
-      </c>
-      <c r="D90" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E90" s="3" t="inlineStr">
-        <is>
-          <t>/queryRuleSnapshots</t>
-        </is>
-      </c>
-      <c r="F90" s="3" t="n"/>
-      <c r="G90" s="7" t="inlineStr">
-        <is>
-          <t>规则快照查询 — 100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="16" customHeight="1">
-      <c r="A91" s="3" t="n"/>
-      <c r="B91" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C91" s="3" t="inlineStr">
-        <is>
-          <t>history-controller</t>
-        </is>
-      </c>
-      <c r="D91" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E91" s="3" t="inlineStr">
-        <is>
-          <t>/setIgnored</t>
-        </is>
-      </c>
-      <c r="F91" s="3" t="n"/>
-      <c r="G91" s="7" t="inlineStr">
-        <is>
-          <t>设置忽略操作[需TikTok执行历史]（无ES流量）</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="16" customHeight="1">
-      <c r="A92" s="3" t="n"/>
-      <c r="B92" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C92" s="3" t="inlineStr">
-        <is>
-          <t>history-controller</t>
-        </is>
-      </c>
-      <c r="D92" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E92" s="3" t="inlineStr">
-        <is>
-          <t>/setRemarks</t>
-        </is>
-      </c>
-      <c r="F92" s="3" t="n"/>
-      <c r="G92" s="7" t="inlineStr">
-        <is>
-          <t>设置执行日志备注[需TikTok执行历史]（无ES流量）</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="16" customHeight="1">
-      <c r="A93" s="3" t="n"/>
-      <c r="B93" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C93" s="3" t="inlineStr">
-        <is>
-          <t>migration-controller</t>
-        </is>
-      </c>
-      <c r="D93" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E93" s="3" t="inlineStr">
-        <is>
-          <t>/migration/amazon/targetingType</t>
-        </is>
-      </c>
-      <c r="F93" s="3" t="n"/>
-      <c r="G93" s="7" t="inlineStr">
-        <is>
-          <t>Amazon定向类型迁移（无ES流量）</t>
-        </is>
-      </c>
-    </row>
-    <row r="94" ht="16" customHeight="1">
-      <c r="A94" s="3" t="n"/>
-      <c r="B94" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C94" s="3" t="inlineStr">
-        <is>
-          <t>migration-controller</t>
-        </is>
-      </c>
-      <c r="D94" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E94" s="3" t="inlineStr">
-        <is>
-          <t>/migration/kroger-to-krogerv3</t>
-        </is>
-      </c>
-      <c r="F94" s="3" t="n"/>
-      <c r="G94" s="7" t="inlineStr">
-        <is>
-          <t>Kroger迁移至KrogerV3 — 2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="16" customHeight="1">
-      <c r="A95" s="3" t="n"/>
-      <c r="B95" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C95" s="3" t="inlineStr">
-        <is>
-          <t>migration-controller</t>
-        </is>
-      </c>
-      <c r="D95" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E95" s="3" t="inlineStr">
-        <is>
-          <t>/migration/single-to-multi-action</t>
-        </is>
-      </c>
-      <c r="F95" s="3" t="n"/>
-      <c r="G95" s="7" t="inlineStr">
-        <is>
-          <t>单动作迁移至多动作（无ES流量）</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="16" customHeight="1">
-      <c r="A96" s="3" t="n"/>
-      <c r="B96" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C96" s="3" t="inlineStr">
-        <is>
-          <t>report-controller</t>
-        </is>
-      </c>
-      <c r="D96" s="3" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="E96" s="3" t="inlineStr">
-        <is>
-          <t>/profitero/getProfiteroCountryList</t>
-        </is>
-      </c>
-      <c r="F96" s="3" t="n"/>
-      <c r="G96" s="7" t="inlineStr">
-        <is>
-          <t>获取Profitero国家列表 — 52%</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="16" customHeight="1">
-      <c r="A97" s="3" t="n"/>
-      <c r="B97" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C97" s="3" t="inlineStr">
-        <is>
-          <t>report-controller</t>
-        </is>
-      </c>
-      <c r="D97" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E97" s="3" t="inlineStr">
-        <is>
-          <t>/report/BrandEventList</t>
-        </is>
-      </c>
-      <c r="F97" s="3" t="n"/>
-      <c r="G97" s="7" t="inlineStr">
-        <is>
-          <t>walmart平台品牌事件列表 — 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="16" customHeight="1">
-      <c r="A98" s="3" t="n"/>
-      <c r="B98" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C98" s="3" t="inlineStr">
-        <is>
-          <t>report-controller</t>
-        </is>
-      </c>
-      <c r="D98" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E98" s="3" t="inlineStr">
-        <is>
-          <t>/report/CompetitorBrandSummary</t>
-        </is>
-      </c>
-      <c r="F98" s="3" t="n"/>
-      <c r="G98" s="7" t="inlineStr">
-        <is>
-          <t>walmart平台竞争品牌汇总</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="16" customHeight="1">
-      <c r="A99" s="3" t="n"/>
-      <c r="B99" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C99" s="3" t="inlineStr">
-        <is>
-          <t>report-controller</t>
-        </is>
-      </c>
-      <c r="D99" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E99" s="3" t="inlineStr">
-        <is>
-          <t>/report/ExecutionRecordSummary</t>
-        </is>
-      </c>
-      <c r="F99" s="3" t="n"/>
-      <c r="G99" s="7" t="inlineStr">
-        <is>
-          <t>target平台执行记录汇总 — 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="16" customHeight="1">
-      <c r="A100" s="3" t="n"/>
-      <c r="B100" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C100" s="3" t="inlineStr">
-        <is>
-          <t>report-controller</t>
-        </is>
-      </c>
-      <c r="D100" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E100" s="3" t="inlineStr">
-        <is>
-          <t>/report/getAllBrands</t>
-        </is>
-      </c>
-      <c r="F100" s="3" t="n"/>
-      <c r="G100" s="7" t="inlineStr">
-        <is>
-          <t>walmart平台获取所有品牌</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="16" customHeight="1">
-      <c r="A101" s="3" t="n"/>
-      <c r="B101" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C101" s="3" t="inlineStr">
-        <is>
-          <t>report-controller</t>
-        </is>
-      </c>
-      <c r="D101" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E101" s="3" t="inlineStr">
-        <is>
-          <t>/report/getAllProfiteroRules</t>
-        </is>
-      </c>
-      <c r="F101" s="3" t="n"/>
-      <c r="G101" s="7" t="inlineStr">
-        <is>
-          <t>获取所有Profitero规则</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="16" customHeight="1">
-      <c r="A102" s="3" t="n"/>
-      <c r="B102" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C102" s="3" t="inlineStr">
-        <is>
-          <t>report-controller</t>
-        </is>
-      </c>
-      <c r="D102" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E102" s="3" t="inlineStr">
-        <is>
-          <t>/report/getAllProfiteroRulesApplies</t>
-        </is>
-      </c>
-      <c r="F102" s="3" t="n"/>
-      <c r="G102" s="7" t="inlineStr">
-        <is>
-          <t>查询Profitero规则应用记录 — 7%</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="16" customHeight="1">
-      <c r="A103" s="3" t="n"/>
-      <c r="B103" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C103" s="3" t="inlineStr">
-        <is>
-          <t>report-controller</t>
-        </is>
-      </c>
-      <c r="D103" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E103" s="3" t="inlineStr">
-        <is>
-          <t>/report/getAsins</t>
-        </is>
-      </c>
-      <c r="F103" s="3" t="n"/>
-      <c r="G103" s="7" t="inlineStr">
-        <is>
-          <t>walmart平台获取ASIN列表 — 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="104" ht="16" customHeight="1">
-      <c r="A104" s="3" t="n"/>
-      <c r="B104" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C104" s="3" t="inlineStr">
-        <is>
-          <t>report-controller</t>
-        </is>
-      </c>
-      <c r="D104" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E104" s="3" t="inlineStr">
-        <is>
-          <t>/report/getDailyRuleData</t>
-        </is>
-      </c>
-      <c r="F104" s="3" t="n"/>
-      <c r="G104" s="7" t="inlineStr">
-        <is>
-          <t>查询每日规则数据</t>
-        </is>
-      </c>
-    </row>
-    <row r="105" ht="16" customHeight="1">
-      <c r="A105" s="3" t="n"/>
-      <c r="B105" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C105" s="3" t="inlineStr">
-        <is>
-          <t>report-controller</t>
-        </is>
-      </c>
-      <c r="D105" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E105" s="3" t="inlineStr">
-        <is>
-          <t>/report/getSignals</t>
-        </is>
-      </c>
-      <c r="F105" s="3" t="n"/>
-      <c r="G105" s="7" t="inlineStr">
-        <is>
-          <t>amazon平台获取信号数据 — 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" ht="16" customHeight="1">
-      <c r="A106" s="3" t="n"/>
-      <c r="B106" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C106" s="3" t="inlineStr">
-        <is>
-          <t>report-controller</t>
-        </is>
-      </c>
-      <c r="D106" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E106" s="3" t="inlineStr">
-        <is>
-          <t>/report/MyBrandCountSummary</t>
-        </is>
-      </c>
-      <c r="F106" s="3" t="n"/>
-      <c r="G106" s="7" t="inlineStr">
-        <is>
-          <t>target平台我的品牌数量汇总 — 6%</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="16" customHeight="1">
-      <c r="A107" s="3" t="n"/>
-      <c r="B107" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C107" s="3" t="inlineStr">
-        <is>
-          <t>report-controller</t>
-        </is>
-      </c>
-      <c r="D107" s="3" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="E107" s="3" t="inlineStr">
-        <is>
-          <t>/report/syncBrands</t>
-        </is>
-      </c>
-      <c r="F107" s="3" t="n"/>
-      <c r="G107" s="7" t="inlineStr">
-        <is>
-          <t>同步品牌数据 — 16%</t>
-        </is>
-      </c>
-    </row>
-    <row r="108" ht="16" customHeight="1">
-      <c r="A108" s="3" t="n"/>
-      <c r="B108" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C108" s="3" t="inlineStr">
-        <is>
-          <t>report-controller</t>
-        </is>
-      </c>
-      <c r="D108" s="3" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="E108" s="3" t="inlineStr">
-        <is>
-          <t>/report/syncTables</t>
-        </is>
-      </c>
-      <c r="F108" s="3" t="n"/>
-      <c r="G108" s="7" t="inlineStr">
-        <is>
-          <t>同步表格数据 — 16%</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="16" customHeight="1">
-      <c r="A109" s="3" t="n"/>
-      <c r="B109" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C109" s="3" t="inlineStr">
-        <is>
-          <t>share-pass-controller</t>
-        </is>
-      </c>
-      <c r="D109" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E109" s="3" t="inlineStr">
-        <is>
-          <t>/sharePass/check</t>
-        </is>
-      </c>
-      <c r="F109" s="3" t="n"/>
-      <c r="G109" s="7" t="inlineStr">
-        <is>
-          <t>校验共享通行证有效性 — 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="110" ht="16" customHeight="1">
-      <c r="A110" s="3" t="n"/>
-      <c r="B110" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C110" s="3" t="inlineStr">
-        <is>
-          <t>share-pass-controller</t>
-        </is>
-      </c>
-      <c r="D110" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E110" s="3" t="inlineStr">
-        <is>
-          <t>/sharePass/create</t>
-        </is>
-      </c>
-      <c r="F110" s="3" t="n"/>
-      <c r="G110" s="7" t="inlineStr">
-        <is>
-          <t>创建共享通行证后删除（可重复） — 8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="111" ht="16" customHeight="1">
-      <c r="A111" s="3" t="n"/>
-      <c r="B111" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C111" s="3" t="inlineStr">
-        <is>
-          <t>share-pass-controller</t>
-        </is>
-      </c>
-      <c r="D111" s="3" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="E111" s="3" t="inlineStr">
-        <is>
-          <t>/sharePass/creators</t>
-        </is>
-      </c>
-      <c r="F111" s="3" t="n"/>
-      <c r="G111" s="7" t="inlineStr">
-        <is>
-          <t>获取创建者列表 — 23%</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="3" t="n"/>
-      <c r="B112" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C112" s="3" t="inlineStr">
-        <is>
-          <t>share-pass-controller</t>
-        </is>
-      </c>
-      <c r="D112" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E112" s="3" t="inlineStr">
-        <is>
-          <t>/sharePass/delete</t>
-        </is>
-      </c>
-      <c r="F112" s="3" t="n"/>
-      <c r="G112" s="3" t="n"/>
-    </row>
-    <row r="113" ht="16" customHeight="1">
-      <c r="A113" s="3" t="n"/>
-      <c r="B113" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C113" s="3" t="inlineStr">
-        <is>
-          <t>share-pass-controller</t>
-        </is>
-      </c>
-      <c r="D113" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E113" s="3" t="inlineStr">
-        <is>
-          <t>/sharePass/edit</t>
-        </is>
-      </c>
-      <c r="F113" s="3" t="n"/>
-      <c r="G113" s="7" t="inlineStr">
-        <is>
-          <t>编辑共享通行证（无ES流量）</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="16" customHeight="1">
-      <c r="A114" s="3" t="n"/>
-      <c r="B114" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C114" s="3" t="inlineStr">
-        <is>
-          <t>share-pass-controller</t>
-        </is>
-      </c>
-      <c r="D114" s="3" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="E114" s="3" t="inlineStr">
-        <is>
-          <t>/sharePass/getAccounts</t>
-        </is>
-      </c>
-      <c r="F114" s="3" t="n"/>
-      <c r="G114" s="7" t="inlineStr">
-        <is>
-          <t>获取可共享账户列表 — 25%</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="16" customHeight="1">
-      <c r="A115" s="3" t="n"/>
-      <c r="B115" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C115" s="3" t="inlineStr">
-        <is>
-          <t>share-pass-controller</t>
-        </is>
-      </c>
-      <c r="D115" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E115" s="3" t="inlineStr">
-        <is>
-          <t>/sharePass/getRuleIdsFromSharePass</t>
-        </is>
-      </c>
-      <c r="F115" s="3" t="n"/>
-      <c r="G115" s="7" t="inlineStr">
-        <is>
-          <t>通过共享通行证获取规则ID列表</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="16" customHeight="1">
-      <c r="A116" s="3" t="n"/>
-      <c r="B116" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C116" s="3" t="inlineStr">
-        <is>
-          <t>share-pass-controller</t>
-        </is>
-      </c>
-      <c r="D116" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E116" s="3" t="inlineStr">
-        <is>
-          <t>/sharePass/getSharePlatforms</t>
-        </is>
-      </c>
-      <c r="F116" s="3" t="n"/>
-      <c r="G116" s="7" t="inlineStr">
-        <is>
-          <t>获取可共享平台列表 — 8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="117" ht="16" customHeight="1">
-      <c r="A117" s="3" t="n"/>
-      <c r="B117" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C117" s="3" t="inlineStr">
-        <is>
-          <t>share-pass-controller</t>
-        </is>
-      </c>
-      <c r="D117" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E117" s="3" t="inlineStr">
-        <is>
-          <t>/sharePass/list</t>
-        </is>
-      </c>
-      <c r="F117" s="3" t="n"/>
-      <c r="G117" s="7" t="inlineStr">
-        <is>
-          <t>amazon平台分页查询共享通行证列表 — 24%</t>
-        </is>
-      </c>
-    </row>
-    <row r="118" ht="16" customHeight="1">
-      <c r="A118" s="3" t="n"/>
-      <c r="B118" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C118" s="3" t="inlineStr">
-        <is>
-          <t>template-controller</t>
-        </is>
-      </c>
-      <c r="D118" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E118" s="3" t="inlineStr">
-        <is>
-          <t>/template</t>
-        </is>
-      </c>
-      <c r="F118" s="3" t="n"/>
-      <c r="G118" s="7" t="inlineStr">
-        <is>
-          <t>创建模板并批量创建(可重复)</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="16" customHeight="1">
-      <c r="A119" s="3" t="n"/>
-      <c r="B119" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C119" s="3" t="inlineStr">
-        <is>
-          <t>template-controller</t>
-        </is>
-      </c>
-      <c r="D119" s="3" t="inlineStr">
-        <is>
-          <t>DELETE</t>
-        </is>
-      </c>
-      <c r="E119" s="3" t="inlineStr">
-        <is>
-          <t>/template/{templateId}</t>
-        </is>
-      </c>
-      <c r="F119" s="3" t="n"/>
-      <c r="G119" s="7" t="inlineStr">
-        <is>
-          <t>删除模板（需有效templateId）</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="16" customHeight="1">
-      <c r="A120" s="3" t="n"/>
-      <c r="B120" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C120" s="3" t="inlineStr">
-        <is>
-          <t>template-controller</t>
-        </is>
-      </c>
-      <c r="D120" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E120" s="3" t="inlineStr">
-        <is>
-          <t>/template/addFavorite</t>
-        </is>
-      </c>
-      <c r="F120" s="3" t="n"/>
-      <c r="G120" s="7" t="inlineStr">
-        <is>
-          <t>模板收藏切换</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="3" t="n"/>
-      <c r="B121" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C121" s="3" t="inlineStr">
-        <is>
-          <t>template-controller</t>
-        </is>
-      </c>
-      <c r="D121" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E121" s="3" t="inlineStr">
-        <is>
-          <t>/template/bulk</t>
-        </is>
-      </c>
-      <c r="F121" s="3" t="n"/>
-      <c r="G121" s="3" t="n"/>
-    </row>
-    <row r="122" ht="16" customHeight="1">
-      <c r="A122" s="3" t="n"/>
-      <c r="B122" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C122" s="3" t="inlineStr">
-        <is>
-          <t>template-controller</t>
-        </is>
-      </c>
-      <c r="D122" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E122" s="3" t="inlineStr">
-        <is>
-          <t>/template/category</t>
-        </is>
-      </c>
-      <c r="F122" s="3" t="n"/>
-      <c r="G122" s="7" t="inlineStr">
-        <is>
-          <t>创建编辑删除分类(可重复)</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="3" t="n"/>
-      <c r="B123" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C123" s="3" t="inlineStr">
-        <is>
-          <t>template-controller</t>
-        </is>
-      </c>
-      <c r="D123" s="3" t="inlineStr">
-        <is>
-          <t>DELETE</t>
-        </is>
-      </c>
-      <c r="E123" s="3" t="inlineStr">
-        <is>
-          <t>/template/category/{categoryId}</t>
-        </is>
-      </c>
-      <c r="F123" s="3" t="n"/>
-      <c r="G123" s="3" t="n"/>
-    </row>
-    <row r="124" ht="16" customHeight="1">
-      <c r="A124" s="3" t="n"/>
-      <c r="B124" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C124" s="3" t="inlineStr">
-        <is>
-          <t>template-controller</t>
-        </is>
-      </c>
-      <c r="D124" s="3" t="inlineStr">
-        <is>
-          <t>DELETE</t>
-        </is>
-      </c>
-      <c r="E124" s="3" t="inlineStr">
-        <is>
-          <t>/template/default/{templateId}</t>
-        </is>
-      </c>
-      <c r="F124" s="3" t="n"/>
-      <c r="G124" s="7" t="inlineStr">
-        <is>
-          <t>默认模板/分类删除接口覆盖</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="3" t="n"/>
-      <c r="B125" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C125" s="3" t="inlineStr">
-        <is>
-          <t>template-controller</t>
-        </is>
-      </c>
-      <c r="D125" s="3" t="inlineStr">
-        <is>
-          <t>DELETE</t>
-        </is>
-      </c>
-      <c r="E125" s="3" t="inlineStr">
-        <is>
-          <t>/template/defaultCategory/{categoryId}</t>
-        </is>
-      </c>
-      <c r="F125" s="3" t="n"/>
-      <c r="G125" s="3" t="n"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="3" t="n"/>
-      <c r="B126" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C126" s="3" t="inlineStr">
-        <is>
-          <t>template-controller</t>
-        </is>
-      </c>
-      <c r="D126" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E126" s="3" t="inlineStr">
-        <is>
-          <t>/template/editCategory</t>
-        </is>
-      </c>
-      <c r="F126" s="3" t="n"/>
-      <c r="G126" s="3" t="n"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="3" t="n"/>
-      <c r="B127" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C127" s="3" t="inlineStr">
-        <is>
-          <t>template-controller</t>
-        </is>
-      </c>
-      <c r="D127" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E127" s="3" t="inlineStr">
-        <is>
-          <t>/template/editDefaultCategory</t>
-        </is>
-      </c>
-      <c r="F127" s="3" t="n"/>
-      <c r="G127" s="3" t="n"/>
-    </row>
-    <row r="128" ht="16" customHeight="1">
-      <c r="A128" s="3" t="n"/>
-      <c r="B128" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C128" s="3" t="inlineStr">
-        <is>
-          <t>template-controller</t>
-        </is>
-      </c>
-      <c r="D128" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E128" s="3" t="inlineStr">
-        <is>
-          <t>/template/editDefaultTemplate</t>
-        </is>
-      </c>
-      <c r="F128" s="3" t="n"/>
-      <c r="G128" s="7" t="inlineStr">
-        <is>
-          <t>查询并尝试编辑系统默认模板</t>
-        </is>
-      </c>
-    </row>
-    <row r="129" ht="16" customHeight="1">
-      <c r="A129" s="3" t="n"/>
-      <c r="B129" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C129" s="3" t="inlineStr">
-        <is>
-          <t>template-controller</t>
-        </is>
-      </c>
-      <c r="D129" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E129" s="3" t="inlineStr">
-        <is>
-          <t>/template/editTemplate</t>
-        </is>
-      </c>
-      <c r="F129" s="3" t="n"/>
-      <c r="G129" s="7" t="inlineStr">
-        <is>
-          <t>创建模板并验证editTemplate端点可达(可重复)</t>
-        </is>
-      </c>
-    </row>
-    <row r="130" ht="32" customHeight="1">
-      <c r="A130" s="3" t="n"/>
-      <c r="B130" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C130" s="3" t="inlineStr">
-        <is>
-          <t>template-controller</t>
-        </is>
-      </c>
-      <c r="D130" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E130" s="3" t="inlineStr">
-        <is>
-          <t>/template/getCategory</t>
-        </is>
-      </c>
-      <c r="F130" s="3" t="n"/>
-      <c r="G130" s="7" t="inlineStr">
-        <is>
-          <t>无ruleType过滤查询全部分类 — 40%
-Targeting类型模板分类 — 40%</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="16" customHeight="1">
-      <c r="A131" s="3" t="n"/>
-      <c r="B131" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C131" s="3" t="inlineStr">
-        <is>
-          <t>template-controller</t>
-        </is>
-      </c>
-      <c r="D131" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E131" s="3" t="inlineStr">
-        <is>
-          <t>/template/getDefaultCategory</t>
-        </is>
-      </c>
-      <c r="F131" s="3" t="n"/>
-      <c r="G131" s="7" t="inlineStr">
-        <is>
-          <t>获取默认模板分类 — 0.11%</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="16" customHeight="1">
-      <c r="A132" s="3" t="n"/>
-      <c r="B132" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C132" s="3" t="inlineStr">
-        <is>
-          <t>template-controller</t>
-        </is>
-      </c>
-      <c r="D132" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E132" s="3" t="inlineStr">
-        <is>
-          <t>/template/getDefaultTemplate</t>
-        </is>
-      </c>
-      <c r="F132" s="3" t="n"/>
-      <c r="G132" s="7" t="inlineStr">
-        <is>
-          <t>获取默认模板列表 — 0.15%</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" ht="16" customHeight="1">
-      <c r="A133" s="3" t="n"/>
-      <c r="B133" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C133" s="3" t="inlineStr">
-        <is>
-          <t>template-controller</t>
-        </is>
-      </c>
-      <c r="D133" s="3" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="E133" s="3" t="inlineStr">
-        <is>
-          <t>/template/getOwners</t>
-        </is>
-      </c>
-      <c r="F133" s="3" t="n"/>
-      <c r="G133" s="7" t="inlineStr">
-        <is>
-          <t>获取模板创建者列表 — 3%</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="3" t="n"/>
-      <c r="B134" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C134" s="3" t="inlineStr">
-        <is>
-          <t>template-controller</t>
-        </is>
-      </c>
-      <c r="D134" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E134" s="3" t="inlineStr">
-        <is>
-          <t>/template/getRecommendation</t>
-        </is>
-      </c>
-      <c r="F134" s="3" t="n"/>
-      <c r="G134" s="3" t="n"/>
-    </row>
-    <row r="135" ht="16" customHeight="1">
-      <c r="A135" s="3" t="n"/>
-      <c r="B135" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C135" s="3" t="inlineStr">
-        <is>
-          <t>template-controller</t>
-        </is>
-      </c>
-      <c r="D135" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E135" s="3" t="inlineStr">
-        <is>
-          <t>/template/getTemplate</t>
-        </is>
-      </c>
-      <c r="F135" s="3" t="n"/>
-      <c r="G135" s="7" t="inlineStr">
-        <is>
-          <t>onlyFavorite:true查询收藏模板 — 47%</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="16" customHeight="1">
-      <c r="A136" s="3" t="n"/>
-      <c r="B136" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C136" s="3" t="inlineStr">
-        <is>
-          <t>template-controller</t>
-        </is>
-      </c>
-      <c r="D136" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E136" s="3" t="inlineStr">
-        <is>
-          <t>/template/getTemplateListFromDirectShare</t>
-        </is>
-      </c>
-      <c r="F136" s="3" t="n"/>
-      <c r="G136" s="7" t="inlineStr">
-        <is>
-          <t>通过直链分享获取模板列表</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="16" customHeight="1">
-      <c r="A137" s="3" t="n"/>
-      <c r="B137" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C137" s="3" t="inlineStr">
-        <is>
-          <t>template-controller</t>
-        </is>
-      </c>
-      <c r="D137" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E137" s="3" t="inlineStr">
-        <is>
-          <t>/template/getTemplateListFromSharePass</t>
-        </is>
-      </c>
-      <c r="F137" s="3" t="n"/>
-      <c r="G137" s="7" t="inlineStr">
-        <is>
-          <t>通过分享密码获取模板列表 — 0.09%</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="16" customHeight="1">
-      <c r="A138" s="3" t="n"/>
-      <c r="B138" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C138" s="3" t="inlineStr">
-        <is>
-          <t>template-controller</t>
-        </is>
-      </c>
-      <c r="D138" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E138" s="3" t="inlineStr">
-        <is>
-          <t>/template/moveDefaultTemplate</t>
-        </is>
-      </c>
-      <c r="F138" s="3" t="n"/>
-      <c r="G138" s="7" t="inlineStr">
-        <is>
-          <t>移动默认模板到分类</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="16" customHeight="1">
-      <c r="A139" s="3" t="n"/>
-      <c r="B139" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C139" s="3" t="inlineStr">
-        <is>
-          <t>template-controller</t>
-        </is>
-      </c>
-      <c r="D139" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E139" s="3" t="inlineStr">
-        <is>
-          <t>/template/moveTemplate</t>
-        </is>
-      </c>
-      <c r="F139" s="3" t="n"/>
-      <c r="G139" s="7" t="inlineStr">
-        <is>
-          <t>移动模板到分类(创建临时分类,可重复)</t>
-        </is>
-      </c>
-    </row>
-    <row r="140" ht="16" customHeight="1">
-      <c r="A140" s="3" t="n"/>
-      <c r="B140" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C140" s="3" t="inlineStr">
-        <is>
-          <t>to-event</t>
-        </is>
-      </c>
-      <c r="D140" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E140" s="3" t="inlineStr">
-        <is>
-          <t>/event/clearCacheTypes</t>
-        </is>
-      </c>
-      <c r="F140" s="3" t="n"/>
-      <c r="G140" s="7" t="inlineStr">
-        <is>
-          <t>清除规则缓存类型(无ES流量)（无ES流量）</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="16" customHeight="1">
-      <c r="A141" s="3" t="n"/>
-      <c r="B141" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C141" s="3" t="inlineStr">
-        <is>
-          <t>to-event</t>
-        </is>
-      </c>
-      <c r="D141" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E141" s="3" t="inlineStr">
-        <is>
-          <t>/event/getRuleCountByCampaignIds</t>
-        </is>
-      </c>
-      <c r="F141" s="3" t="n"/>
-      <c r="G141" s="7" t="inlineStr">
-        <is>
-          <t>按campaignId统计规则数量(无ES流量,TikTok返回405)（无ES流量）</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="16" customHeight="1">
-      <c r="A142" s="3" t="n"/>
-      <c r="B142" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C142" s="3" t="inlineStr">
-        <is>
-          <t>to-event</t>
-        </is>
-      </c>
-      <c r="D142" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E142" s="3" t="inlineStr">
-        <is>
-          <t>/event/getRuleCountByUserIds</t>
-        </is>
-      </c>
-      <c r="F142" s="3" t="n"/>
-      <c r="G142" s="7" t="inlineStr">
-        <is>
-          <t>按userId统计TikTok规则数量 — 100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="16" customHeight="1">
-      <c r="A143" s="3" t="n"/>
-      <c r="B143" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C143" s="3" t="inlineStr">
-        <is>
-          <t>to-event</t>
-        </is>
-      </c>
-      <c r="D143" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E143" s="3" t="inlineStr">
-        <is>
-          <t>/event/getRuleDefinition</t>
-        </is>
-      </c>
-      <c r="F143" s="3" t="n"/>
-      <c r="G143" s="7" t="inlineStr">
-        <is>
-          <t>按ruleIds批量获取规则定义(创建临时规则,可重复) — 100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="16" customHeight="1">
-      <c r="A144" s="3" t="n"/>
-      <c r="B144" s="3" t="inlineStr">
-        <is>
-          <t>amazon</t>
-        </is>
-      </c>
-      <c r="C144" s="3" t="inlineStr">
-        <is>
-          <t>to-event</t>
-        </is>
-      </c>
-      <c r="D144" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E144" s="3" t="inlineStr">
-        <is>
-          <t>/event/getRuleTypes</t>
-        </is>
-      </c>
-      <c r="F144" s="3" t="n"/>
-      <c r="G144" s="7" t="inlineStr">
-        <is>
-          <t>获取规则类型列表 — 100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="145" ht="16" customHeight="1">
-      <c r="A145" s="3" t="n"/>
-      <c r="B145" s="3" t="inlineStr">
-        <is>
-          <t>tiktok</t>
-        </is>
-      </c>
-      <c r="C145" s="3" t="inlineStr">
-        <is>
-          <t>auto-task-controller</t>
-        </is>
-      </c>
-      <c r="D145" s="3" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="E145" s="3" t="inlineStr">
-        <is>
-          <t>/task/sendManualRuleMessage</t>
-        </is>
-      </c>
-      <c r="F145" s="3" t="n"/>
-      <c r="G145" s="7" t="inlineStr">
-        <is>
-          <t>手动触发规则消息（无ES流量）</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="16" customHeight="1">
-      <c r="A146" s="3" t="n"/>
-      <c r="B146" s="3" t="inlineStr">
-        <is>
-          <t>tiktok</t>
-        </is>
-      </c>
-      <c r="C146" s="3" t="inlineStr">
-        <is>
-          <t>config-controller</t>
-        </is>
-      </c>
-      <c r="D146" s="3" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="E146" s="3" t="inlineStr">
-        <is>
-          <t>/config/actionMetrics</t>
-        </is>
-      </c>
-      <c r="F146" s="3" t="n"/>
-      <c r="G146" s="7" t="inlineStr">
-        <is>
-          <t>获取规则动作执行指标 — 100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="147" ht="16" customHeight="1">
-      <c r="A147" s="3" t="n"/>
-      <c r="B147" s="3" t="inlineStr">
-        <is>
-          <t>tiktok</t>
-        </is>
-      </c>
-      <c r="C147" s="3" t="inlineStr">
-        <is>
-          <t>config-controller</t>
-        </is>
-      </c>
-      <c r="D147" s="3" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="E147" s="3" t="inlineStr">
-        <is>
-          <t>/config/emails</t>
-        </is>
-      </c>
-      <c r="F147" s="3" t="n"/>
-      <c r="G147" s="7" t="inlineStr">
-        <is>
-          <t>获取规则通知邮件列表 — 100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="16" customHeight="1">
-      <c r="A148" s="3" t="n"/>
-      <c r="B148" s="3" t="inlineStr">
-        <is>
-          <t>tiktok</t>
-        </is>
-      </c>
-      <c r="C148" s="3" t="inlineStr">
-        <is>
-          <t>config-controller</t>
-        </is>
-      </c>
-      <c r="D148" s="3" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="E148" s="3" t="inlineStr">
-        <is>
-          <t>/config/getAddOn</t>
-        </is>
-      </c>
-      <c r="F148" s="3" t="n"/>
-      <c r="G148" s="7" t="inlineStr">
-        <is>
-          <t>获取AddOn插件状态（无ES流量）</t>
-        </is>
-      </c>
-    </row>
-    <row r="149" ht="16" customHeight="1">
-      <c r="A149" s="3" t="n"/>
-      <c r="B149" s="3" t="inlineStr">
-        <is>
-          <t>tiktok</t>
-        </is>
-      </c>
-      <c r="C149" s="3" t="inlineStr">
-        <is>
-          <t>config-controller</t>
-        </is>
-      </c>
-      <c r="D149" s="3" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="E149" s="3" t="inlineStr">
-        <is>
-          <t>/config/getCommercePermission</t>
-        </is>
-      </c>
-      <c r="F149" s="3" t="n"/>
-      <c r="G149" s="7" t="inlineStr">
-        <is>
-          <t>获取商业化功能权限 — 100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="16" customHeight="1">
-      <c r="A150" s="3" t="n"/>
-      <c r="B150" s="3" t="inlineStr">
-        <is>
-          <t>tiktok</t>
-        </is>
-      </c>
-      <c r="C150" s="3" t="inlineStr">
-        <is>
-          <t>config-controller</t>
-        </is>
-      </c>
-      <c r="D150" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E150" s="3" t="inlineStr">
-        <is>
-          <t>/config/openAddOn</t>
-        </is>
-      </c>
-      <c r="F150" s="3" t="n"/>
-      <c r="G150" s="7" t="inlineStr">
-        <is>
-          <t>开通AddOn插件 [NEEDS REAL VALUE]（无ES流量）</t>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="16" customHeight="1">
-      <c r="A151" s="3" t="n"/>
-      <c r="B151" s="3" t="inlineStr">
-        <is>
-          <t>tiktok</t>
-        </is>
-      </c>
-      <c r="C151" s="3" t="inlineStr">
-        <is>
-          <t>config-controller</t>
-        </is>
-      </c>
-      <c r="D151" s="3" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="E151" s="3" t="inlineStr">
-        <is>
-          <t>/config/requirementMetrics</t>
-        </is>
-      </c>
-      <c r="F151" s="3" t="n"/>
-      <c r="G151" s="7" t="inlineStr">
-        <is>
-          <t>获取规则条件指标配置 — 100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="152" ht="32" customHeight="1">
-      <c r="A152" s="3" t="n"/>
-      <c r="B152" s="3" t="inlineStr">
-        <is>
-          <t>tiktok</t>
-        </is>
-      </c>
-      <c r="C152" s="3" t="inlineStr">
-        <is>
-          <t>config-controller</t>
-        </is>
-      </c>
-      <c r="D152" s="3" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="E152" s="3" t="inlineStr">
-        <is>
-          <t>/config/RuleActionMetrics</t>
-        </is>
-      </c>
-      <c r="F152" s="3" t="n"/>
-      <c r="G152" s="7" t="inlineStr">
-        <is>
-          <t>获取规则动作指标配置 — 100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="153" ht="32" customHeight="1">
-      <c r="A153" s="3" t="n"/>
-      <c r="B153" s="3" t="inlineStr">
-        <is>
-          <t>tiktok</t>
-        </is>
-      </c>
-      <c r="C153" s="3" t="inlineStr">
-        <is>
-          <t>config-controller</t>
-        </is>
-      </c>
-      <c r="D153" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E153" s="3" t="inlineStr">
-        <is>
-          <t>/config/RuleActionMetrics</t>
-        </is>
-      </c>
-      <c r="F153" s="3" t="n"/>
-      <c r="G153" s="7" t="inlineStr">
-        <is>
-          <t>保存自定义规则动作指标配置（无ES流量）</t>
-        </is>
-      </c>
-    </row>
-    <row r="154" ht="16" customHeight="1">
-      <c r="A154" s="3" t="n"/>
-      <c r="B154" s="3" t="inlineStr">
-        <is>
-          <t>tiktok</t>
-        </is>
-      </c>
-      <c r="C154" s="3" t="inlineStr">
-        <is>
-          <t>config-controller</t>
-        </is>
-      </c>
-      <c r="D154" s="3" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="E154" s="3" t="inlineStr">
-        <is>
-          <t>/config/ruleTypes</t>
-        </is>
-      </c>
-      <c r="F154" s="3" t="n"/>
-      <c r="G154" s="7" t="inlineStr">
-        <is>
-          <t>获取规则类型枚举列表 — 100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="155" ht="16" customHeight="1">
-      <c r="A155" s="3" t="n"/>
-      <c r="B155" s="3" t="inlineStr">
-        <is>
-          <t>tiktok</t>
-        </is>
-      </c>
-      <c r="C155" s="3" t="inlineStr">
-        <is>
-          <t>config-controller</t>
-        </is>
-      </c>
-      <c r="D155" s="3" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="E155" s="3" t="inlineStr">
-        <is>
-          <t>/config/supportedTimeZones</t>
-        </is>
-      </c>
-      <c r="F155" s="3" t="n"/>
-      <c r="G155" s="7" t="inlineStr">
-        <is>
-          <t>获取支持的时区列表 — 100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="16" customHeight="1">
-      <c r="A156" s="3" t="n"/>
-      <c r="B156" s="3" t="inlineStr">
-        <is>
-          <t>tiktok</t>
-        </is>
-      </c>
-      <c r="C156" s="3" t="inlineStr">
-        <is>
-          <t>data-impact-controller</t>
-        </is>
-      </c>
-      <c r="D156" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E156" s="3" t="inlineStr">
-        <is>
-          <t>/dataImpact/brandOrManufacturers</t>
-        </is>
-      </c>
-      <c r="F156" s="3" t="n"/>
-      <c r="G156" s="7" t="inlineStr">
-        <is>
-          <t>查询品牌/制造商数据（无ES流量）</t>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="16" customHeight="1">
-      <c r="A157" s="3" t="n"/>
-      <c r="B157" s="3" t="inlineStr">
-        <is>
-          <t>tiktok</t>
-        </is>
-      </c>
-      <c r="C157" s="3" t="inlineStr">
-        <is>
-          <t>data-impact-controller</t>
-        </is>
-      </c>
-      <c r="D157" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E157" s="3" t="inlineStr">
-        <is>
-          <t>/dataImpact/categories</t>
-        </is>
-      </c>
-      <c r="F157" s="3" t="n"/>
-      <c r="G157" s="7" t="inlineStr">
-        <is>
-          <t>查询数据影响分类（无ES流量）</t>
-        </is>
-      </c>
-    </row>
-    <row r="158" ht="16" customHeight="1">
-      <c r="A158" s="3" t="n"/>
-      <c r="B158" s="3" t="inlineStr">
-        <is>
-          <t>tiktok</t>
-        </is>
-      </c>
-      <c r="C158" s="3" t="inlineStr">
-        <is>
-          <t>data-impact-controller</t>
-        </is>
-      </c>
-      <c r="D158" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E158" s="3" t="inlineStr">
-        <is>
-          <t>/dataImpact/oos/asinList</t>
-        </is>
-      </c>
-      <c r="F158" s="3" t="n"/>
-      <c r="G158" s="7" t="inlineStr">
-        <is>
-          <t>查询OOS ASIN列表 — 1%</t>
-        </is>
-      </c>
-    </row>
-    <row r="159" ht="16" customHeight="1">
-      <c r="A159" s="3" t="n"/>
-      <c r="B159" s="3" t="inlineStr">
-        <is>
-          <t>tiktok</t>
-        </is>
-      </c>
-      <c r="C159" s="3" t="inlineStr">
-        <is>
-          <t>data-impact-controller</t>
-        </is>
-      </c>
-      <c r="D159" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E159" s="3" t="inlineStr">
-        <is>
-          <t>/dataImpact/oos/brandList</t>
-        </is>
-      </c>
-      <c r="F159" s="3" t="n"/>
-      <c r="G159" s="7" t="inlineStr">
-        <is>
-          <t>查询OOS品牌列表 — 2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="160" ht="16" customHeight="1">
-      <c r="A160" s="3" t="n"/>
-      <c r="B160" s="3" t="inlineStr">
-        <is>
-          <t>tiktok</t>
-        </is>
-      </c>
-      <c r="C160" s="3" t="inlineStr">
-        <is>
-          <t>data-impact-controller</t>
-        </is>
-      </c>
-      <c r="D160" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E160" s="3" t="inlineStr">
-        <is>
-          <t>/dataImpact/price/asinList</t>
-        </is>
-      </c>
-      <c r="F160" s="3" t="n"/>
-      <c r="G160" s="7" t="inlineStr">
-        <is>
-          <t>查询价格ASIN列表 — 2%</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="3" t="n"/>
-      <c r="B161" s="3" t="inlineStr">
-        <is>
-          <t>tiktok</t>
-        </is>
-      </c>
-      <c r="C161" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D161" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E161" s="3" t="inlineStr">
-        <is>
-          <t>/automationPauseAsins</t>
-        </is>
-      </c>
-      <c r="F161" s="3" t="n"/>
-      <c r="G161" s="8" t="inlineStr">
-        <is>
-          <t>TikTok 平台无生产流量，暂不生成 case</t>
-        </is>
-      </c>
-    </row>
-    <row r="162" ht="16" customHeight="1">
-      <c r="A162" s="3" t="n"/>
-      <c r="B162" s="3" t="inlineStr">
-        <is>
-          <t>tiktok</t>
-        </is>
-      </c>
-      <c r="C162" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D162" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E162" s="3" t="inlineStr">
-        <is>
-          <t>/bulk-create/tiktok/roas-explorer</t>
-        </is>
-      </c>
-      <c r="F162" s="3" t="n"/>
-      <c r="G162" s="7" t="inlineStr">
-        <is>
-          <t>批量创建TikTok RoasExplorer规则(含后置删除,可重复) — 100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="3" t="n"/>
-      <c r="B163" s="3" t="inlineStr">
-        <is>
-          <t>tiktok</t>
-        </is>
-      </c>
-      <c r="C163" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D163" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E163" s="3" t="inlineStr">
-        <is>
-          <t>/bulk-create/tiktok/smart-budget-boost</t>
-        </is>
-      </c>
-      <c r="F163" s="3" t="n"/>
-      <c r="G163" s="8" t="inlineStr">
-        <is>
-          <t>TikTok 平台无生产流量，暂不生成 case</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="3" t="n"/>
-      <c r="B164" s="3" t="inlineStr">
-        <is>
-          <t>tiktok</t>
-        </is>
-      </c>
-      <c r="C164" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D164" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E164" s="3" t="inlineStr">
-        <is>
-          <t>/bulkCreateRule</t>
-        </is>
-      </c>
-      <c r="F164" s="3" t="n"/>
-      <c r="G164" s="8" t="inlineStr">
-        <is>
-          <t>TikTok 平台无生产流量，暂不生成 case</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="3" t="n"/>
-      <c r="B165" s="3" t="inlineStr">
-        <is>
-          <t>tiktok</t>
-        </is>
-      </c>
-      <c r="C165" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D165" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E165" s="3" t="inlineStr">
-        <is>
-          <t>/createAdtomicRule</t>
-        </is>
-      </c>
-      <c r="F165" s="3" t="n"/>
-      <c r="G165" s="8" t="inlineStr">
-        <is>
-          <t>TikTok 平台无生产流量，暂不生成 case</t>
-        </is>
-      </c>
-    </row>
-    <row r="166" ht="16" customHeight="1">
-      <c r="A166" s="3" t="n"/>
-      <c r="B166" s="3" t="inlineStr">
-        <is>
-          <t>tiktok</t>
-        </is>
-      </c>
-      <c r="C166" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D166" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E166" s="3" t="inlineStr">
-        <is>
-          <t>/definition</t>
-        </is>
-      </c>
-      <c r="F166" s="3" t="n"/>
-      <c r="G166" s="7" t="inlineStr">
-        <is>
-          <t>创建TikTok BudgetBoost规则(含后置删除,可重复) — 100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="167" ht="16" customHeight="1">
-      <c r="A167" s="3" t="n"/>
-      <c r="B167" s="3" t="inlineStr">
-        <is>
-          <t>tiktok</t>
-        </is>
-      </c>
-      <c r="C167" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D167" s="3" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="E167" s="3" t="inlineStr">
-        <is>
-          <t>/definition/{ruleId}</t>
-        </is>
-      </c>
-      <c r="F167" s="3" t="n"/>
-      <c r="G167" s="3" t="n"/>
-    </row>
-    <row r="168">
-      <c r="A168" s="3" t="n"/>
-      <c r="B168" s="3" t="inlineStr">
-        <is>
-          <t>tiktok</t>
-        </is>
-      </c>
-      <c r="C168" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D168" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E168" s="3" t="inlineStr">
-        <is>
-          <t>/definition/addAppliedObj</t>
-        </is>
-      </c>
-      <c r="F168" s="3" t="n"/>
-      <c r="G168" s="8" t="inlineStr">
-        <is>
-          <t>TikTok 平台无生产流量，暂不生成 case</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="3" t="n"/>
-      <c r="B169" s="3" t="inlineStr">
-        <is>
-          <t>tiktok</t>
-        </is>
-      </c>
-      <c r="C169" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D169" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E169" s="3" t="inlineStr">
-        <is>
-          <t>/definition/addAppliedObjBySeparateRule</t>
-        </is>
-      </c>
-      <c r="F169" s="3" t="n"/>
-      <c r="G169" s="8" t="inlineStr">
-        <is>
-          <t>TikTok 平台无生产流量，暂不生成 case</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="3" t="n"/>
-      <c r="B170" s="3" t="inlineStr">
-        <is>
-          <t>tiktok</t>
-        </is>
-      </c>
-      <c r="C170" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D170" s="3" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="E170" s="3" t="inlineStr">
-        <is>
-          <t>/definition/adtomic/{adtomicRuleId}</t>
-        </is>
-      </c>
-      <c r="F170" s="3" t="n"/>
-      <c r="G170" s="8" t="inlineStr">
-        <is>
-          <t>TikTok 平台无生产流量，暂不生成 case</t>
-        </is>
-      </c>
-    </row>
-    <row r="171" ht="16" customHeight="1">
-      <c r="A171" s="3" t="n"/>
-      <c r="B171" s="3" t="inlineStr">
-        <is>
-          <t>tiktok</t>
-        </is>
-      </c>
-      <c r="C171" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D171" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E171" s="3" t="inlineStr">
-        <is>
-          <t>/definition/adtomicRules/settings</t>
-        </is>
-      </c>
-      <c r="F171" s="3" t="n"/>
-      <c r="G171" s="8" t="inlineStr">
-        <is>
-          <t>TikTok 平台无生产流量，暂不生成 case</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="3" t="n"/>
-      <c r="B172" s="3" t="inlineStr">
-        <is>
-          <t>tiktok</t>
-        </is>
-      </c>
-      <c r="C172" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D172" s="3" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="E172" s="3" t="inlineStr">
-        <is>
-          <t>/definition/adtomicRules/settings/{profileId}</t>
-        </is>
-      </c>
-      <c r="F172" s="3" t="n"/>
-      <c r="G172" s="8" t="inlineStr">
-        <is>
-          <t>TikTok 平台无生产流量，暂不生成 case</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" s="3" t="n"/>
-      <c r="B173" s="3" t="inlineStr">
-        <is>
-          <t>tiktok</t>
-        </is>
-      </c>
-      <c r="C173" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D173" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E173" s="3" t="inlineStr">
-        <is>
-          <t>/definition/calculateNextExecutionTime</t>
-        </is>
-      </c>
-      <c r="F173" s="3" t="n"/>
-      <c r="G173" s="8" t="inlineStr">
-        <is>
-          <t>TikTok 平台无生产流量，暂不生成 case</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" s="3" t="n"/>
-      <c r="B174" s="3" t="inlineStr">
-        <is>
-          <t>tiktok</t>
-        </is>
-      </c>
-      <c r="C174" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D174" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E174" s="3" t="inlineStr">
-        <is>
-          <t>/definition/changeOwners</t>
-        </is>
-      </c>
-      <c r="F174" s="3" t="n"/>
-      <c r="G174" s="8" t="inlineStr">
-        <is>
-          <t>TikTok 平台无生产流量，暂不生成 case</t>
-        </is>
-      </c>
-    </row>
-    <row r="175" ht="16" customHeight="1">
-      <c r="A175" s="3" t="n"/>
-      <c r="B175" s="3" t="inlineStr">
-        <is>
-          <t>tiktok</t>
-        </is>
-      </c>
-      <c r="C175" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D175" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E175" s="3" t="inlineStr">
-        <is>
-          <t>/definition/changeStatus</t>
-        </is>
-      </c>
-      <c r="F175" s="3" t="n"/>
-      <c r="G175" s="7" t="inlineStr">
-        <is>
-          <t>暂停/恢复规则(创建临时规则,可重复) — 40%</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" s="3" t="n"/>
-      <c r="B176" s="3" t="inlineStr">
-        <is>
-          <t>tiktok</t>
-        </is>
-      </c>
-      <c r="C176" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D176" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E176" s="3" t="inlineStr">
-        <is>
-          <t>/definition/checkAutoRefillRule</t>
-        </is>
-      </c>
-      <c r="F176" s="3" t="n"/>
-      <c r="G176" s="8" t="inlineStr">
-        <is>
-          <t>TikTok 平台无生产流量，暂不生成 case</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" s="3" t="n"/>
-      <c r="B177" s="3" t="inlineStr">
-        <is>
-          <t>tiktok</t>
-        </is>
-      </c>
-      <c r="C177" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D177" s="3" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="E177" s="3" t="inlineStr">
-        <is>
-          <t>/definition/checkCustom/{ruleId}</t>
-        </is>
-      </c>
-      <c r="F177" s="3" t="n"/>
-      <c r="G177" s="8" t="inlineStr">
-        <is>
-          <t>TikTok 平台无生产流量，暂不生成 case</t>
-        </is>
-      </c>
-    </row>
-    <row r="178" ht="32" customHeight="1">
-      <c r="A178" s="3" t="n"/>
-      <c r="B178" s="3" t="inlineStr">
-        <is>
-          <t>tiktok</t>
-        </is>
-      </c>
-      <c r="C178" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D178" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E178" s="3" t="inlineStr">
-        <is>
-          <t>/definition/checkRuleName</t>
-        </is>
-      </c>
-      <c r="F178" s="3" t="n"/>
-      <c r="G178" s="7" t="inlineStr">
-        <is>
-          <t>新建规则名称重复校验 — 80%
-编辑规则名称重复校验(创建临时规则,可重复) — 20%</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" s="3" t="n"/>
-      <c r="B179" s="3" t="inlineStr">
-        <is>
-          <t>tiktok</t>
-        </is>
-      </c>
-      <c r="C179" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D179" s="3" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="E179" s="3" t="inlineStr">
-        <is>
-          <t>/definition/commerceRuleClient</t>
-        </is>
-      </c>
-      <c r="F179" s="3" t="n"/>
-      <c r="G179" s="8" t="inlineStr">
-        <is>
-          <t>TikTok 平台无生产流量，暂不生成 case</t>
-        </is>
-      </c>
-    </row>
-    <row r="180" ht="16" customHeight="1">
-      <c r="A180" s="3" t="n"/>
-      <c r="B180" s="3" t="inlineStr">
-        <is>
-          <t>tiktok</t>
-        </is>
-      </c>
-      <c r="C180" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D180" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E180" s="3" t="inlineStr">
-        <is>
-          <t>/definition/commerceRuleReport</t>
-        </is>
-      </c>
-      <c r="F180" s="3" t="n"/>
-      <c r="G180" s="8" t="inlineStr">
-        <is>
-          <t>TikTok 平台无生产流量，暂不生成 case</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" s="3" t="n"/>
-      <c r="B181" s="3" t="inlineStr">
-        <is>
-          <t>tiktok</t>
-        </is>
-      </c>
-      <c r="C181" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D181" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E181" s="3" t="inlineStr">
-        <is>
-          <t>/definition/delete/{adtomicRuleId}</t>
-        </is>
-      </c>
-      <c r="F181" s="3" t="n"/>
-      <c r="G181" s="8" t="inlineStr">
-        <is>
-          <t>TikTok 平台无生产流量，暂不生成 case</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" s="3" t="n"/>
-      <c r="B182" s="3" t="inlineStr">
-        <is>
-          <t>tiktok</t>
-        </is>
-      </c>
-      <c r="C182" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D182" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E182" s="3" t="inlineStr">
-        <is>
-          <t>/definition/editAdtomicRule</t>
-        </is>
-      </c>
-      <c r="F182" s="3" t="n"/>
-      <c r="G182" s="8" t="inlineStr">
-        <is>
-          <t>TikTok 平台无生产流量，暂不生成 case</t>
-        </is>
-      </c>
-    </row>
-    <row r="183" ht="32" customHeight="1">
-      <c r="A183" s="3" t="n"/>
-      <c r="B183" s="3" t="inlineStr">
-        <is>
-          <t>tiktok</t>
-        </is>
-      </c>
-      <c r="C183" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D183" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E183" s="3" t="inlineStr">
-        <is>
-          <t>/definition/editRule</t>
-        </is>
-      </c>
-      <c r="F183" s="3" t="n"/>
-      <c r="G183" s="7" t="inlineStr">
-        <is>
-          <t>编辑TikTok Campaign级规则(创建临时规则,可重复) — 100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" s="3" t="n"/>
-      <c r="B184" s="3" t="inlineStr">
-        <is>
-          <t>tiktok</t>
-        </is>
-      </c>
-      <c r="C184" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D184" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E184" s="3" t="inlineStr">
-        <is>
-          <t>/definition/export</t>
-        </is>
-      </c>
-      <c r="F184" s="3" t="n"/>
-      <c r="G184" s="8" t="inlineStr">
-        <is>
-          <t>TikTok 平台无生产流量，暂不生成 case</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" s="3" t="n"/>
-      <c r="B185" s="3" t="inlineStr">
-        <is>
-          <t>tiktok</t>
-        </is>
-      </c>
-      <c r="C185" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D185" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E185" s="3" t="inlineStr">
-        <is>
-          <t>/definition/export/commerceRuleReport</t>
-        </is>
-      </c>
-      <c r="F185" s="3" t="n"/>
-      <c r="G185" s="8" t="inlineStr">
-        <is>
-          <t>TikTok 平台无生产流量，暂不生成 case</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" s="3" t="n"/>
-      <c r="B186" s="3" t="inlineStr">
-        <is>
-          <t>tiktok</t>
-        </is>
-      </c>
-      <c r="C186" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D186" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E186" s="3" t="inlineStr">
-        <is>
-          <t>/definition/getAdtomicRules</t>
-        </is>
-      </c>
-      <c r="F186" s="3" t="n"/>
-      <c r="G186" s="8" t="inlineStr">
-        <is>
-          <t>TikTok 平台无生产流量，暂不生成 case</t>
-        </is>
-      </c>
-    </row>
-    <row r="187" ht="16" customHeight="1">
-      <c r="A187" s="3" t="n"/>
-      <c r="B187" s="3" t="inlineStr">
-        <is>
-          <t>tiktok</t>
-        </is>
-      </c>
-      <c r="C187" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D187" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E187" s="3" t="inlineStr">
-        <is>
-          <t>/definition/getApplyRule</t>
-        </is>
-      </c>
-      <c r="F187" s="3" t="n"/>
-      <c r="G187" s="7" t="inlineStr">
-        <is>
-          <t>查询规则应用列表 — 100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="188" ht="16" customHeight="1">
-      <c r="A188" s="3" t="n"/>
-      <c r="B188" s="3" t="inlineStr">
-        <is>
-          <t>tiktok</t>
-        </is>
-      </c>
-      <c r="C188" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D188" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E188" s="3" t="inlineStr">
-        <is>
-          <t>/definition/getAsinRelatedRule</t>
-        </is>
-      </c>
-      <c r="F188" s="3" t="n"/>
-      <c r="G188" s="8" t="inlineStr">
-        <is>
-          <t>TikTok 平台无生产流量，暂不生成 case</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" s="3" t="n"/>
-      <c r="B189" s="3" t="inlineStr">
-        <is>
-          <t>tiktok</t>
-        </is>
-      </c>
-      <c r="C189" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D189" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E189" s="3" t="inlineStr">
-        <is>
-          <t>/definition/getAutoRefillRuleApplyTagCampaigns</t>
-        </is>
-      </c>
-      <c r="F189" s="3" t="n"/>
-      <c r="G189" s="8" t="inlineStr">
-        <is>
-          <t>TikTok 平台无生产流量，暂不生成 case</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="3" t="n"/>
-      <c r="B190" s="3" t="inlineStr">
-        <is>
-          <t>tiktok</t>
-        </is>
-      </c>
-      <c r="C190" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D190" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E190" s="3" t="inlineStr">
-        <is>
-          <t>/definition/getAutoRefillRuleApplyTags</t>
-        </is>
-      </c>
-      <c r="F190" s="3" t="n"/>
-      <c r="G190" s="8" t="inlineStr">
-        <is>
-          <t>TikTok 平台无生产流量，暂不生成 case</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="3" t="n"/>
-      <c r="B191" s="3" t="inlineStr">
-        <is>
-          <t>tiktok</t>
-        </is>
-      </c>
-      <c r="C191" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D191" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E191" s="3" t="inlineStr">
-        <is>
-          <t>/definition/getAutoRefillRuleApplyTargets</t>
-        </is>
-      </c>
-      <c r="F191" s="3" t="n"/>
-      <c r="G191" s="8" t="inlineStr">
-        <is>
-          <t>TikTok 平台无生产流量，暂不生成 case</t>
-        </is>
-      </c>
-    </row>
-    <row r="192" ht="16" customHeight="1">
-      <c r="A192" s="3" t="n"/>
-      <c r="B192" s="3" t="inlineStr">
-        <is>
-          <t>tiktok</t>
-        </is>
-      </c>
-      <c r="C192" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D192" s="3" t="inlineStr">
-        <is>
-          <t>GET</t>
-        </is>
-      </c>
-      <c r="E192" s="3" t="inlineStr">
-        <is>
-          <t>/definition/getAutoRefillRuleProfileIds</t>
-        </is>
-      </c>
-      <c r="F192" s="3" t="n"/>
-      <c r="G192" s="7" t="inlineStr">
-        <is>
-          <t>查询AutoRefill规则关联profile — 100%</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="3" t="n"/>
-      <c r="B193" s="3" t="inlineStr">
-        <is>
-          <t>tiktok</t>
-        </is>
-      </c>
-      <c r="C193" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D193" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E193" s="3" t="inlineStr">
-        <is>
-          <t>/definition/getCampaignWithRule</t>
-        </is>
-      </c>
-      <c r="F193" s="3" t="n"/>
-      <c r="G193" s="8" t="inlineStr">
-        <is>
-          <t>TikTok 平台无生产流量，暂不生成 case</t>
-        </is>
-      </c>
-    </row>
-    <row r="194" ht="48" customHeight="1">
-      <c r="A194" s="3" t="n"/>
-      <c r="B194" s="3" t="inlineStr">
-        <is>
-          <t>tiktok</t>
-        </is>
-      </c>
-      <c r="C194" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D194" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E194" s="3" t="inlineStr">
-        <is>
-          <t>/definition/getOwners</t>
-        </is>
-      </c>
-      <c r="F194" s="3" t="n"/>
-      <c r="G194" s="7" t="inlineStr">
-        <is>
-          <t>Auto模式获取规则负责人 — 42%
-Manual模式获取规则负责人 — 30%
-AutoCommerce模式获取规则负责人 — 20%</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="3" t="n"/>
-      <c r="B195" s="3" t="inlineStr">
-        <is>
-          <t>tiktok</t>
-        </is>
-      </c>
-      <c r="C195" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D195" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E195" s="3" t="inlineStr">
-        <is>
-          <t>/definition/getProfile</t>
-        </is>
-      </c>
-      <c r="F195" s="3" t="n"/>
-      <c r="G195" s="8" t="inlineStr">
-        <is>
-          <t>TikTok 平台无生产流量，暂不生成 case</t>
-        </is>
-      </c>
-    </row>
-    <row r="196" ht="48" customHeight="1">
-      <c r="A196" s="3" t="n"/>
-      <c r="B196" s="3" t="inlineStr">
-        <is>
-          <t>tiktok</t>
-        </is>
-      </c>
-      <c r="C196" s="3" t="inlineStr">
-        <is>
-          <t>definition-controller</t>
-        </is>
-      </c>
-      <c r="D196" s="3" t="inlineStr">
-        <is>
-          <t>POST</t>
-        </is>
-      </c>
-      <c r="E196" s="3" t="inlineStr">
-        <is>
-          <t>/definition/getRule</t>
-        </is>
-      </c>
-      <c r="F196" s="3" t="n"/>
-      <c r="G196" s="7" t="inlineStr">
-        <is>
-          <t>Auto模式默认规则列表 — 53%
-按ruleIds精确查询(创建临时规则,可重复) — 22%
-Manual模式规则列表 — 12%</t>
-        </is>
-      </c>
-    </row>
     <row r="197" ht="16" customHeight="1">
       <c r="A197" s="3" t="n"/>
       <c r="B197" s="3" t="inlineStr">
@@ -12361,11 +12518,11 @@
       <c r="F293" s="3" t="n"/>
       <c r="G293" s="7" t="inlineStr">
         <is>
-          <t>手动触发规则消息（无ES流量）</t>
-        </is>
-      </c>
-    </row>
-    <row r="294" ht="16" customHeight="1">
+          <t>场景1: 默认调用(无入参)</t>
+        </is>
+      </c>
+    </row>
+    <row r="294" ht="64" customHeight="1">
       <c r="A294" s="3" t="n"/>
       <c r="B294" s="3" t="inlineStr">
         <is>
@@ -12390,7 +12547,10 @@
       <c r="F294" s="3" t="n"/>
       <c r="G294" s="7" t="inlineStr">
         <is>
-          <t>获取规则动作执行指标 — 100%</t>
+          <t>场景1: ruleType=Keyword
+场景2: ruleType=Item
+场景3: ruleType=Campaign
+场景4: ruleType=SOV Bid</t>
         </is>
       </c>
     </row>
@@ -12419,7 +12579,7 @@
       <c r="F295" s="3" t="n"/>
       <c r="G295" s="7" t="inlineStr">
         <is>
-          <t>获取规则通知邮件列表 — 100%</t>
+          <t>场景1: 默认调用(无入参)</t>
         </is>
       </c>
     </row>
@@ -12448,7 +12608,7 @@
       <c r="F296" s="3" t="n"/>
       <c r="G296" s="7" t="inlineStr">
         <is>
-          <t>获取AddOn插件状态（无ES流量）</t>
+          <t>场景1: 默认调用(无入参)</t>
         </is>
       </c>
     </row>
@@ -12477,7 +12637,7 @@
       <c r="F297" s="3" t="n"/>
       <c r="G297" s="7" t="inlineStr">
         <is>
-          <t>获取商业化功能权限 — 100%</t>
+          <t>场景1: 默认调用(无入参)</t>
         </is>
       </c>
     </row>
@@ -12506,7 +12666,7 @@
       <c r="F298" s="3" t="n"/>
       <c r="G298" s="7" t="inlineStr">
         <is>
-          <t>开通AddOn插件 [NEEDS REAL VALUE]（无ES流量）</t>
+          <t>场景1: productLine=walmart</t>
         </is>
       </c>
     </row>
@@ -12535,7 +12695,7 @@
       <c r="F299" s="3" t="n"/>
       <c r="G299" s="7" t="inlineStr">
         <is>
-          <t>获取规则条件指标配置 — 100%</t>
+          <t>场景1: ruleType=Keyword(推断)</t>
         </is>
       </c>
     </row>
@@ -12564,7 +12724,7 @@
       <c r="F300" s="3" t="n"/>
       <c r="G300" s="7" t="inlineStr">
         <is>
-          <t>获取规则动作指标配置 — 100%</t>
+          <t>场景1: 默认调用(无入参)</t>
         </is>
       </c>
     </row>
@@ -12593,7 +12753,7 @@
       <c r="F301" s="3" t="n"/>
       <c r="G301" s="7" t="inlineStr">
         <is>
-          <t>保存自定义规则动作指标配置（无ES流量）</t>
+          <t>场景1: productLine=walmart</t>
         </is>
       </c>
     </row>
@@ -12622,7 +12782,7 @@
       <c r="F302" s="3" t="n"/>
       <c r="G302" s="7" t="inlineStr">
         <is>
-          <t>获取规则类型枚举列表 — 100%</t>
+          <t>场景1: productLine=walmart筛选</t>
         </is>
       </c>
     </row>
@@ -12651,7 +12811,7 @@
       <c r="F303" s="3" t="n"/>
       <c r="G303" s="7" t="inlineStr">
         <is>
-          <t>获取支持的时区列表 — 100%</t>
+          <t>场景1: 默认调用(无入参)</t>
         </is>
       </c>
     </row>
@@ -12680,7 +12840,7 @@
       <c r="F304" s="3" t="n"/>
       <c r="G304" s="7" t="inlineStr">
         <is>
-          <t>查询品牌/制造商数据（无ES流量）</t>
+          <t>场景1: productLine=walmart默认场景</t>
         </is>
       </c>
     </row>
@@ -12709,7 +12869,7 @@
       <c r="F305" s="3" t="n"/>
       <c r="G305" s="7" t="inlineStr">
         <is>
-          <t>查询数据影响分类（无ES流量）</t>
+          <t>场景1: productLine=walmart</t>
         </is>
       </c>
     </row>
@@ -12738,7 +12898,7 @@
       <c r="F306" s="3" t="n"/>
       <c r="G306" s="7" t="inlineStr">
         <is>
-          <t>查询OOS ASIN列表 — 1%</t>
+          <t>场景1: 默认查询(walmart构造)</t>
         </is>
       </c>
     </row>
@@ -12767,7 +12927,7 @@
       <c r="F307" s="3" t="n"/>
       <c r="G307" s="7" t="inlineStr">
         <is>
-          <t>查询OOS品牌列表 — 2%</t>
+          <t>场景1: productLine=walmart</t>
         </is>
       </c>
     </row>
@@ -12796,7 +12956,7 @@
       <c r="F308" s="3" t="n"/>
       <c r="G308" s="7" t="inlineStr">
         <is>
-          <t>查询价格ASIN列表 — 2%</t>
+          <t>场景1: productLine=walmart</t>
         </is>
       </c>
     </row>
